--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.9%</t>
+          <t>-68.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.0%</t>
+          <t>-518.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-183.0%</t>
+          <t>-179.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-53.8%</t>
         </is>
       </c>
     </row>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.7632133785488</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.766007000080281</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.766669348471939</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.765749825212049</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.83208537900887</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.540666251398268</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.610956483720444</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.625584219836487</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.624120200661159</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.622611818701087</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.622474686136524</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.616868480275114</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.623250237302918</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.628142610677643</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.614897283153515</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.618994985764144</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
         <v>2.623155925395222</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405955</v>
       </c>
       <c r="C1983" t="n">
         <v>2.629035527923059</v>
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.590953117728553</v>
+        <v>-3.412587474771743</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.190707856987138</v>
+        <v>1.262054114169862</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3651834589743241</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.824190085122391</v>
+        <v>2.846555603776901</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.611011196593393</v>
+        <v>-3.432645553636583</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.233932390624242</v>
+        <v>1.305278647806966</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3651834589743241</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.87543785030543</v>
+        <v>2.897803368959941</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.571080523415503</v>
+        <v>-3.392714880458692</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.248345364489651</v>
+        <v>1.319691621672375</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.3678382677280296</v>
+        <v>0.4051141321522145</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.897836958806417</v>
+        <v>2.920202477460928</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475134</v>
       </c>
       <c r="C1987" t="n">
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.520048430692975</v>
+        <v>-3.341682787736164</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.263706429816932</v>
+        <v>1.335052686999656</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4188703604505576</v>
+        <v>0.4561462248747424</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.923404442678204</v>
+        <v>2.945769961332715</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.454824249565769</v>
+        <v>-3.276458606608958</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.306983506360519</v>
+        <v>1.378329763543244</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.4840945415777632</v>
+        <v>0.5213704060019481</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.979726355447232</v>
+        <v>3.002091874101743</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.417397229494636</v>
+        <v>-3.239031586537825</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.317915286688253</v>
+        <v>1.389261543870977</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.4893460796069449</v>
+        <v>0.5266219440311297</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.978838250564022</v>
+        <v>3.001203769218533</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.437508885529344</v>
+        <v>-3.259143242572533</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.31112741660561</v>
+        <v>1.382473673788335</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5003734246043641</v>
+        <v>0.5376492890285489</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.986711449893714</v>
+        <v>3.009076968548225</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.383764071102139</v>
+        <v>-3.205398428145328</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.493183113397703</v>
+        <v>1.564529370580427</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.510436734044826</v>
+        <v>0.5477125984690109</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.153307206579202</v>
+        <v>3.175672725233713</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.359972502495997</v>
+        <v>-3.181606859539186</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.622812650057977</v>
+        <v>1.694158907240701</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5342283026509683</v>
+        <v>0.5715041670751532</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.287695056960704</v>
+        <v>3.310060575615215</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.333888418232189</v>
+        <v>-3.155522775275378</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.624954259777359</v>
+        <v>1.696300516960084</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5342283026509683</v>
+        <v>0.5715041670751532</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.279403032974563</v>
+        <v>3.301768551629074</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.255757237383242</v>
+        <v>-3.077391594426431</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.654399927700717</v>
+        <v>1.725746184883442</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6084051135346529</v>
+        <v>0.6456809779588377</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.322102315088554</v>
+        <v>3.344467833743064</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.246864775989959</v>
+        <v>-3.068499133033148</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.675511317984822</v>
+        <v>1.746857575167546</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6084051135346529</v>
+        <v>0.6456809779588377</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.339656720815345</v>
+        <v>3.362022239469856</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.415340892959837</v>
+        <v>-3.236975250003026</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.599975918601455</v>
+        <v>1.671322175784179</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.5804572778180721</v>
+        <v>0.6177331422422569</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.31474306678998</v>
+        <v>3.337108585444491</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.717541364098254</v>
+        <v>-2.539175721141443</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.86036542733395</v>
+        <v>1.931711684516674</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5101092184476614</v>
+        <v>0.5473850828718463</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.253803928355596</v>
+        <v>3.276169447010107</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.694820260415101</v>
+        <v>-2.51645461745829</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.860117891304115</v>
+        <v>1.93146414848684</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5101092184476614</v>
+        <v>0.5473850828718463</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.2444679508525</v>
+        <v>3.266833469507011</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.693095217125057</v>
+        <v>-2.514729574168246</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.019714034471302</v>
+        <v>2.091060291654026</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.5118342617377052</v>
+        <v>0.54911012616189</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.404409102677695</v>
+        <v>3.426774621332207</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.847876223903312</v>
+        <v>-2.669510580946501</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.994879454253646</v>
+        <v>2.066225711436371</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.4784665876832291</v>
+        <v>0.5157424521074139</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.421466320738657</v>
+        <v>3.443831839393167</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.796440890518653</v>
+        <v>-2.618075247561842</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.012128943597055</v>
+        <v>2.08347520077978</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5299019210678888</v>
+        <v>0.5671777854920735</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.449002876758998</v>
+        <v>3.471368395413508</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.769489666192165</v>
+        <v>-2.591124023235354</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.032915586972392</v>
+        <v>2.104261844155117</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.544782267095608</v>
+        <v>0.5820581315197927</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.467937238020371</v>
+        <v>3.490302756674881</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.905442674248481</v>
+        <v>-2.72707703129167</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.162637515894826</v>
+        <v>2.23398377307755</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.544782267095608</v>
+        <v>0.5820581315197927</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.65204037016533</v>
+        <v>3.674405888819841</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.927850792053353</v>
+        <v>-2.749485149096542</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.14579096367587</v>
+        <v>2.217137220858594</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.544782267095608</v>
+        <v>0.5820581315197927</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.644157065068323</v>
+        <v>3.666522583722834</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.075856559532752</v>
+        <v>-2.897490916575942</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.088642656233747</v>
+        <v>2.159988913416472</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4580552582320665</v>
+        <v>0.4953311226562512</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.594174859299836</v>
+        <v>3.616540377954347</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.085297485421282</v>
+        <v>-2.906931842464472</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.141120003600183</v>
+        <v>2.212466260782907</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.5804823757754579</v>
+        <v>0.6177582401996426</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.723884847547718</v>
+        <v>3.746250366202229</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.084010721881726</v>
+        <v>-2.905645078924915</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.144525803561306</v>
+        <v>2.21587206074403</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5817691393150145</v>
+        <v>0.6190450037391992</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.727548000216753</v>
+        <v>3.749913518871264</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.085567775871017</v>
+        <v>-2.907202132914207</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.142014794859365</v>
+        <v>2.213361052042089</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5817691393150145</v>
+        <v>0.6190450037391992</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.725659813110528</v>
+        <v>3.748025331765039</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.092839661394482</v>
+        <v>-2.914474018437671</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.133926270252841</v>
+        <v>2.205272527435565</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5744972537915498</v>
+        <v>0.6117731182157344</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.716116911399312</v>
+        <v>3.738482430053822</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.090998642336231</v>
+        <v>-2.91263299937942</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.133096688086294</v>
+        <v>2.204442945269018</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6130413448872029</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.715311857612345</v>
+        <v>3.737677376266856</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.097907347835911</v>
+        <v>-2.919541704879101</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.14340661275234</v>
+        <v>2.214752869935065</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6130413448872029</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.728385264478264</v>
+        <v>3.750750783132774</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.099468990650771</v>
+        <v>-2.92110334769396</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.142781955626397</v>
+        <v>2.214128212809121</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6130413448872029</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.728385264478264</v>
+        <v>3.750750783132774</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.127369777760244</v>
+        <v>-2.949004134803433</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.130145681909609</v>
+        <v>2.201491939092334</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5411685563200834</v>
+        <v>0.5784444207442681</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.706151151119505</v>
+        <v>3.728516669774015</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.130402775272918</v>
+        <v>-2.952037132316107</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.125696926881739</v>
+        <v>2.197043184064463</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5381355588074095</v>
+        <v>0.5754114232315941</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.701095796589099</v>
+        <v>3.72346131524361</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.150464096549425</v>
+        <v>-2.972098453592614</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.18437835796164</v>
+        <v>2.255724615144364</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5180742375309024</v>
+        <v>0.555350101955087</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.755764963413698</v>
+        <v>3.778130482068209</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.407184914544249</v>
+        <v>-3.228819271587438</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.222001749765557</v>
+        <v>2.293348006948281</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4469355278112722</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.831027937929257</v>
+        <v>3.853393456583767</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.842069548909837</v>
+        <v>3.764553669187114</v>
       </c>
       <c r="C2017" t="n">
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.564214272485295</v>
+        <v>-3.565237345893892</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.228170275734778</v>
+        <v>2.22776104637134</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4469355278112722</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.900008207074896</v>
+        <v>3.922373725729408</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.2%</t>
+          <t>-66.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.4%</t>
+          <t>461.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.1%</t>
+          <t>-495.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.4%</t>
+          <t>-144.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-122.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-179.3%</t>
+          <t>-165.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-53.8%</t>
+          <t>-45.2%</t>
         </is>
       </c>
     </row>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.161129235942263</v>
+        <v>-6.934779158359813</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2227081960944424</v>
+        <v>0.3132482271274224</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.056936767473763</v>
+        <v>-0.9143438712046807</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.453354254300837</v>
+        <v>2.538909992062287</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.013189194534664</v>
+        <v>-6.786839116952214</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1620052899693145</v>
+        <v>0.2525453210022945</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.036615851565205</v>
+        <v>-0.8940229552961232</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.345667881157804</v>
+        <v>2.431223618919254</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.960219672280675</v>
+        <v>-6.733869594698225</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1744791126174317</v>
+        <v>0.2650191436504117</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8410534330421343</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.36873560825672</v>
+        <v>2.454291346018169</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.916671265509985</v>
+        <v>-6.690321187927535</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1849378632306147</v>
+        <v>0.2754778942635947</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8410534330421343</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.361774996161627</v>
+        <v>2.447330733923076</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.674522872056126</v>
+        <v>-6.448172794473677</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.296259574993301</v>
+        <v>0.3867996060262811</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8410534330421343</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.37623735054277</v>
+        <v>2.461793088304219</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.566263734933605</v>
+        <v>-6.339913657351155</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3340953503015047</v>
+        <v>0.4246353813344848</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8410534330421343</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.370769471001965</v>
+        <v>2.456325208763414</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.442972600116474</v>
+        <v>-6.216622522534024</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3809098982389338</v>
+        <v>0.4714499292719139</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8603551944940857</v>
+        <v>-0.7177622982250038</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.44224224590282</v>
+        <v>2.527797983664269</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.421823401213031</v>
+        <v>-6.195473323630581</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3970705560376366</v>
+        <v>0.4876105870706162</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.6966130993215605</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.462632743482211</v>
+        <v>2.54818848124366</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.178057959229586</v>
+        <v>-5.951707881647136</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4903574411780647</v>
+        <v>0.5808974722110447</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.6966130993215605</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.458413451829262</v>
+        <v>2.543969189590711</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.076295138952291</v>
+        <v>-5.849945061369842</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.533186883208999</v>
+        <v>0.623726914241979</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6833940309291318</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.468469206784735</v>
+        <v>2.554024944546184</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.826444745003217</v>
+        <v>-5.600094667420767</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6258691157723311</v>
+        <v>0.7164091468053106</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6833940309291318</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.461211281768437</v>
+        <v>2.546767019529886</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.650552652535785</v>
+        <v>-5.424202574953334</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6998250762799523</v>
+        <v>0.7903651073129327</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6833940309291318</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.464810405289086</v>
+        <v>2.550366143050535</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.479106189513321</v>
+        <v>-5.252756111930871</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7817311675434917</v>
+        <v>0.8722711985764717</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6545404641757505</v>
+        <v>-0.5119475679066686</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.581005789157117</v>
+        <v>2.666561526918566</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.404816623774982</v>
+        <v>-5.178466546192531</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8104674714551243</v>
+        <v>0.9010075024881044</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5802508984374113</v>
+        <v>-0.4376580021683293</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624600006216418</v>
+        <v>2.710155743977867</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.341180881541048</v>
+        <v>-5.114830803958597</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8406165694030152</v>
+        <v>0.9311566004359957</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.3740222599343948</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.667476252611096</v>
+        <v>2.753031990372545</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.229754122215128</v>
+        <v>-5.003404044632677</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8663815319171788</v>
+        <v>0.9569215629501593</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.3740222599343948</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.648670511394891</v>
+        <v>2.73422624915634</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.989323625410267</v>
+        <v>-4.762973547827817</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9642968072640004</v>
+        <v>1.054836838296981</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.1335917631295345</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.794671886102685</v>
+        <v>2.880227623864134</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.917081057239073</v>
+        <v>-4.690730979656622</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9971231483672984</v>
+        <v>1.087663179400279</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.1335917631295345</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.798601199937505</v>
+        <v>2.884156937698954</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.864082734957685</v>
+        <v>-4.637732657375234</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.019001061197194</v>
+        <v>1.109541092230174</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.07825550412759569</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.832481539256008</v>
+        <v>2.918037277017458</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.755277849477958</v>
+        <v>-4.528927771895507</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.059521086609078</v>
+        <v>1.150061117642058</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.07825550412759569</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.829479610476002</v>
+        <v>2.915035348237451</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.535257051440947</v>
+        <v>-4.308906973858496</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.149108442834496</v>
+        <v>1.239648473867477</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.07962855532869739</v>
+        <v>0.06296434094038456</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.915790554527404</v>
+        <v>3.001346292288853</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.40238936237767</v>
+        <v>-4.176039284795219</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.218149701261631</v>
+        <v>1.308689732294611</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.07962855532869739</v>
+        <v>0.06296434094038456</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.931684737329228</v>
+        <v>3.017240475090677</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.282216279013171</v>
+        <v>-4.05586620143072</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.267364779047732</v>
+        <v>1.357904810080712</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.04054452803580155</v>
+        <v>0.1831374243048835</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.004934431788229</v>
+        <v>3.090490169549678</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137544133913433</v>
+        <v>-3.911194056330983</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.335321739649067</v>
+        <v>1.425861770682047</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.185216673135539</v>
+        <v>0.3278095694046209</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.101825821409511</v>
+        <v>3.18738155917096</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197418961271126</v>
+        <v>-3.971068883688675</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.297409300107416</v>
+        <v>1.387949331140396</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.2679347420469288</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.051938416396322</v>
+        <v>3.137494154157771</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077598730360289</v>
+        <v>-3.851248652777838</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.360626561705959</v>
+        <v>1.451166592738939</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.2679347420469288</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06722758563053</v>
+        <v>3.152783323391979</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.080068436822095</v>
+        <v>-3.853718359239644</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.267282878443678</v>
+        <v>1.357822909476659</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1228721393160407</v>
+        <v>0.2654650355851226</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.973389961075888</v>
+        <v>3.058945698837337</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148438623146105</v>
+        <v>-3.922088545563653</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.159196665399375</v>
+        <v>1.249736696432356</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2747407346213376</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.898217241982918</v>
+        <v>2.983772979744368</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162226675993152</v>
+        <v>-3.9358765984107</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144118152892448</v>
+        <v>1.234658183925429</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2747407346213376</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.88865395061481</v>
+        <v>2.974209688376259</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.193219835321857</v>
+        <v>-3.966869757739405</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9564304542013529</v>
+        <v>1.046970485234334</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2747407346213376</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.713363515655197</v>
+        <v>2.798919253416646</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.017745575529387</v>
+        <v>-3.791395497946936</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.031187390110128</v>
+        <v>1.121727421143109</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2747407346213376</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.717930747646984</v>
+        <v>2.803486485408433</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.128681828170636</v>
+        <v>-3.902331750588185</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.962554917814836</v>
+        <v>1.053094948847817</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2747407346213376</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.693672776408191</v>
+        <v>2.77922851416964</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.095018282698354</v>
+        <v>-3.868668205115903</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9791517212236545</v>
+        <v>1.069691752256635</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3084042800936194</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.717002288911466</v>
+        <v>2.802558026672915</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.035165663494631</v>
+        <v>-3.80881558591218</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.013265155337276</v>
+        <v>1.103805186370256</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3084042800936194</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.727174675343599</v>
+        <v>2.812730413105048</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.948922200468253</v>
+        <v>-3.722572122885802</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.042708811121687</v>
+        <v>1.133248842154668</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3084042800936194</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.722120945917459</v>
+        <v>2.807676683678908</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.994229019867233</v>
+        <v>-3.767878942284782</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.016361858806621</v>
+        <v>1.106901889839601</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.2675941170843886</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689410623556446</v>
+        <v>2.774966361317895</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.023262124569534</v>
+        <v>-3.796912046987084</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.005300489958802</v>
+        <v>1.095840520991782</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.2675941170843886</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689962496589547</v>
+        <v>2.775518234350996</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.930451643118675</v>
+        <v>-3.704101565536225</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9716973744305115</v>
+        <v>1.062237405463492</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.217811702266166</v>
+        <v>0.360404598535248</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.674921477351428</v>
+        <v>2.760477215112878</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.974841112448102</v>
+        <v>-3.748491034865652</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9558150626233413</v>
+        <v>1.046355093656322</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.1734222329367384</v>
+        <v>0.3160151292058203</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.650161271678373</v>
+        <v>2.735717009439822</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862169894211852</v>
+        <v>-3.635819816629402</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9959592584295645</v>
+        <v>1.086499289462544</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.4286863474420705</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.712839711131846</v>
+        <v>2.798395448893295</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.74979289302918</v>
+        <v>-3.523442815446729</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.046401354733301</v>
+        <v>1.136941385766281</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.4286863474420705</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.718331006962513</v>
+        <v>2.803886744723962</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.777573290930533</v>
+        <v>-3.551223213348083</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.046786397341299</v>
+        <v>1.137326428374279</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2583130532716355</v>
+        <v>0.4009059495407175</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.71315996999024</v>
+        <v>2.79871570775169</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.860574571955812</v>
+        <v>-3.634224494373361</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8519416049318402</v>
+        <v>0.9424816359648203</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3823350650135437</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.540373159274589</v>
+        <v>2.625928897036038</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.969188650399143</v>
+        <v>-3.742838572816693</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9286456342737133</v>
+        <v>1.019185665306694</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3823350650135437</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.660522819993795</v>
+        <v>2.746078557755244</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.933779612151</v>
+        <v>-3.70742953456855</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9573222756752935</v>
+        <v>1.047862306708274</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3823350650135437</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.675035846096118</v>
+        <v>2.760591583857567</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.895395949592849</v>
+        <v>-3.669045872010399</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9700951820409225</v>
+        <v>1.060635213073903</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.4207187275716949</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.695485484973378</v>
+        <v>2.781041222734827</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.718279619557683</v>
+        <v>-3.491929541975233</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.037670742900291</v>
+        <v>1.128210773933271</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.4207187275716949</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.69221451381868</v>
+        <v>2.777770251580129</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.763371864391228</v>
+        <v>-3.537021786808778</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.020317236728786</v>
+        <v>1.110857267761766</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2162297881332231</v>
+        <v>0.3588226844023051</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.655760279678959</v>
+        <v>2.741316017440408</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.58399644315246</v>
+        <v>-3.357646365570011</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.085854380530708</v>
+        <v>1.176394411563688</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3730065463039418</v>
+        <v>0.5155994425730237</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.743613309887805</v>
+        <v>2.829169047649254</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.629010656673067</v>
+        <v>-3.402660579090617</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.048656150454055</v>
+        <v>1.139196181487035</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3426576509893372</v>
+        <v>0.4852505472584191</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.706211428030632</v>
+        <v>2.791767165792081</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.896015166945502</v>
+        <v>-3.669665089363052</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9475459086840265</v>
+        <v>1.038085939717007</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1482946129463886</v>
+        <v>0.2908875092154705</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.595285167543808</v>
+        <v>2.680840905305257</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.997212948382675</v>
+        <v>-3.770862870800225</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9062707180056591</v>
+        <v>0.9968107490386389</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.2224786956701513</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.553443801313118</v>
+        <v>2.638999539074567</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.990701981768362</v>
+        <v>-3.764351904185912</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9064750662057008</v>
+        <v>0.9970150972386806</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.2224786956701513</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.551043762867435</v>
+        <v>2.636599500628884</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.971663854061065</v>
+        <v>-3.745313776478615</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9106150364968646</v>
+        <v>1.001155067529845</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.1642950843389568</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.512658315276963</v>
+        <v>2.598214053038412</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.002790485211683</v>
+        <v>-3.776440407629233</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.075746252975298</v>
+        <v>1.166286284008278</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.1642950843389568</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.690240184215644</v>
+        <v>2.775795921977093</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.0166572465456</v>
+        <v>-3.79030716896315</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.071032877427865</v>
+        <v>1.161572908460844</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.1264371676051338</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.668358763161483</v>
+        <v>2.753914500922932</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.97185307500567</v>
+        <v>-3.745502997423221</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.094963076440763</v>
+        <v>1.185503107473742</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.1264371676051338</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.674367293558409</v>
+        <v>2.759923031319858</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.824110104770668</v>
+        <v>-3.597760027188218</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.233212912326785</v>
+        <v>1.323752943359765</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.294244524840017</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.854204355691361</v>
+        <v>2.93976009345281</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.926124787301889</v>
+        <v>-3.699774709719439</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.195200660845778</v>
+        <v>1.285740691878758</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.294244524840017</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.856997977222842</v>
+        <v>2.942553714984291</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.919972081249105</v>
+        <v>-3.693622003666655</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.19832409165855</v>
+        <v>1.28886412269153</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1578043346237194</v>
+        <v>0.3003972308928013</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.861351949246171</v>
+        <v>2.94690768700762</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.936781379399606</v>
+        <v>-3.710431301817156</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.19068084913846</v>
+        <v>1.28122088017144</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.2835879327422997</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.85034684709598</v>
+        <v>2.93590258485743</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.874483380623484</v>
+        <v>-3.648133303041035</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.281935602445729</v>
+        <v>1.372475633478709</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.2835879327422997</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.916682400892801</v>
+        <v>3.00223813865425</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.540666251398268</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.672693182958326</v>
+        <v>-3.446343105375877</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.07123255390119</v>
+        <v>1.16177258493417</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3390132286423722</v>
+        <v>0.481606124911454</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.744074188583692</v>
+        <v>2.829629926345141</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.610956483720444</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.59931508586959</v>
+        <v>-3.37296500828714</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.17087402505886</v>
+        <v>1.26141405609184</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4123913257311087</v>
+        <v>0.5549842220001906</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.858391279159109</v>
+        <v>2.943947016920558</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.625584219836487</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.697055630494564</v>
+        <v>-3.470705552912114</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.146405543324914</v>
+        <v>1.236945574357894</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3965020475981285</v>
+        <v>0.5390949438672104</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.863485448395365</v>
+        <v>2.949041186156814</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.624120200661159</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.873393390617494</v>
+        <v>-3.647043313035044</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.074406420100414</v>
+        <v>1.164946451133394</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.362757183744281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.756218773146279</v>
+        <v>2.841774510907728</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.622611818701087</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.796971344185567</v>
+        <v>-3.570621266603117</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.103466856713113</v>
+        <v>1.194006887746093</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.362757183744281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.754710391186207</v>
+        <v>2.840266128947656</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.622474686136524</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.752598212546998</v>
+        <v>-3.526248134964548</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.121078976803977</v>
+        <v>1.211619007836957</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.4071303153828496</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.781197137604785</v>
+        <v>2.866752875366234</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.616868480275114</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.629763991659831</v>
+        <v>-3.403413914077381</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.164606459297435</v>
+        <v>1.255146490330414</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.4071303153828496</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.775590931743375</v>
+        <v>2.861146669504824</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.623250237302918</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.582108261098775</v>
+        <v>-3.355758183516325</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.190050508549661</v>
+        <v>1.280590539582641</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3121931496748234</v>
+        <v>0.4547860459439052</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.810566127107812</v>
+        <v>2.896121864869261</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.628142610677643</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.481590102600021</v>
+        <v>-3.255240025017571</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.235150145323888</v>
+        <v>1.325690176356868</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4127113081735779</v>
+        <v>0.5553042044426597</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.87576939558179</v>
+        <v>2.961325133343239</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.614897283153515</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.54225669300241</v>
+        <v>-3.31590661541996</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.197638181638804</v>
+        <v>1.288178212671784</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3310129914550443</v>
+        <v>0.473605887724126</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.813505078026542</v>
+        <v>2.899060815787991</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.618994985764144</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.497418291394012</v>
+        <v>-3.271068213811562</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.219671244892792</v>
+        <v>1.310211275925772</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3355564243999137</v>
+        <v>0.4781493206689955</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.820328840404092</v>
+        <v>2.905884578165542</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.623155925395222</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.59817692715101</v>
+        <v>-3.37182684956856</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.183528730221071</v>
+        <v>1.27406876125405</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2467308556729083</v>
+        <v>0.3893237519419901</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.771194438798967</v>
+        <v>2.856750176560416</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405955</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.629035527923059</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.55397409006511</v>
+        <v>-3.32762401248266</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.207089467583268</v>
+        <v>1.297629498616248</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.2909336927588088</v>
+        <v>0.4335265890278905</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.803595743578345</v>
+        <v>2.889151481339794</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.412587474771743</v>
+        <v>-3.186237397189293</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.262054114169862</v>
+        <v>1.352594145202842</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3651834589743241</v>
+        <v>0.5077763552434059</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.846555603776901</v>
+        <v>2.93211134153835</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.432645553636583</v>
+        <v>-3.206295476054133</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.305278647806966</v>
+        <v>1.395818678839946</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3651834589743241</v>
+        <v>0.5077763552434059</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.897803368959941</v>
+        <v>2.98335910672139</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.392714880458692</v>
+        <v>-3.166364802876243</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.319691621672375</v>
+        <v>1.410231652705355</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.4051141321522145</v>
+        <v>0.5477070284212963</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.920202477460928</v>
+        <v>3.005758215222377</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475134</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.341682787736164</v>
+        <v>-3.115332710153714</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.335052686999656</v>
+        <v>1.425592718032636</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4561462248747424</v>
+        <v>0.5987391211438242</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.945769961332715</v>
+        <v>3.031325699094164</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.276458606608958</v>
+        <v>-3.050108529026509</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.378329763543244</v>
+        <v>1.468869794576224</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.5213704060019481</v>
+        <v>0.6639633022710298</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.002091874101743</v>
+        <v>3.087647611863193</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.239031586537825</v>
+        <v>-3.012681508955375</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.389261543870977</v>
+        <v>1.479801574903957</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.5266219440311297</v>
+        <v>0.6692148403002115</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.001203769218533</v>
+        <v>3.086759506979982</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.259143242572533</v>
+        <v>-3.032793164990083</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.382473673788335</v>
+        <v>1.473013704821315</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5376492890285489</v>
+        <v>0.6802421852976307</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.009076968548225</v>
+        <v>3.094632706309674</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.205398428145328</v>
+        <v>-2.979048350562878</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.564529370580427</v>
+        <v>1.655069401613407</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.5477125984690109</v>
+        <v>0.6903054947380927</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.175672725233713</v>
+        <v>3.261228462995162</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.181606859539186</v>
+        <v>-2.955256781956736</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.694158907240701</v>
+        <v>1.784698938273681</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5715041670751532</v>
+        <v>0.714097063344235</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.310060575615215</v>
+        <v>3.395616313376664</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.155522775275378</v>
+        <v>-2.929172697692928</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.696300516960084</v>
+        <v>1.786840547993063</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5715041670751532</v>
+        <v>0.714097063344235</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.301768551629074</v>
+        <v>3.387324289390523</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.077391594426431</v>
+        <v>-2.851041516843981</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.725746184883442</v>
+        <v>1.816286215916422</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6456809779588377</v>
+        <v>0.7882738742279195</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.344467833743064</v>
+        <v>3.430023571504513</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.068499133033148</v>
+        <v>-2.842149055450698</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.746857575167546</v>
+        <v>1.837397606200526</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6456809779588377</v>
+        <v>0.7882738742279195</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.362022239469856</v>
+        <v>3.447577977231305</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.236975250003026</v>
+        <v>-3.010625172420576</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.671322175784179</v>
+        <v>1.761862206817159</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.6177331422422569</v>
+        <v>0.7603260385113387</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.337108585444491</v>
+        <v>3.42266432320594</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.539175721141443</v>
+        <v>-2.312825643558993</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.931711684516674</v>
+        <v>2.022251715549654</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5473850828718463</v>
+        <v>0.689977979140928</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.276169447010107</v>
+        <v>3.361725184771556</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.51645461745829</v>
+        <v>-2.29010453987584</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.93146414848684</v>
+        <v>2.02200417951982</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5473850828718463</v>
+        <v>0.689977979140928</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.266833469507011</v>
+        <v>3.35238920726846</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.514729574168246</v>
+        <v>-2.288379496585796</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.091060291654026</v>
+        <v>2.181600322687006</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.54911012616189</v>
+        <v>0.6917030224309717</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.426774621332207</v>
+        <v>3.512330359093656</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.669510580946501</v>
+        <v>-2.443160503364052</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.066225711436371</v>
+        <v>2.156765742469351</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.5157424521074139</v>
+        <v>0.6583353483764955</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.443831839393167</v>
+        <v>3.529387577154616</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.618075247561842</v>
+        <v>-2.391725169979392</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.08347520077978</v>
+        <v>2.17401523181276</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5671777854920735</v>
+        <v>0.7097706817611552</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.471368395413508</v>
+        <v>3.556924133174957</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.591124023235354</v>
+        <v>-2.364773945652904</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.104261844155117</v>
+        <v>2.194801875188097</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.5820581315197927</v>
+        <v>0.7246510277888744</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.490302756674881</v>
+        <v>3.57585849443633</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.72707703129167</v>
+        <v>-2.50072695370922</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.23398377307755</v>
+        <v>2.32452380411053</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.5820581315197927</v>
+        <v>0.7246510277888744</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.674405888819841</v>
+        <v>3.75996162658129</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.749485149096542</v>
+        <v>-2.523135071514092</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.217137220858594</v>
+        <v>2.307677251891574</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.5820581315197927</v>
+        <v>0.7246510277888744</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.666522583722834</v>
+        <v>3.752078321484283</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.897490916575942</v>
+        <v>-2.671140838993492</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.159988913416472</v>
+        <v>2.250528944449452</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4953311226562512</v>
+        <v>0.6379240189253329</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.616540377954347</v>
+        <v>3.702096115715796</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.906931842464472</v>
+        <v>-2.680581764882022</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.212466260782907</v>
+        <v>2.303006291815887</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.6177582401996426</v>
+        <v>0.7603511364687243</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.746250366202229</v>
+        <v>3.831806103963678</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.905645078924915</v>
+        <v>-2.679295001342465</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.21587206074403</v>
+        <v>2.30641209177701</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.6190450037391992</v>
+        <v>0.7616379000082809</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.749913518871264</v>
+        <v>3.835469256632713</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.907202132914207</v>
+        <v>-2.680852055331757</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.213361052042089</v>
+        <v>2.303901083075069</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.6190450037391992</v>
+        <v>0.7616379000082809</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.748025331765039</v>
+        <v>3.833581069526488</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.914474018437671</v>
+        <v>-2.688123940855221</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.205272527435565</v>
+        <v>2.295812558468546</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6117731182157344</v>
+        <v>0.7543660144848161</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.738482430053822</v>
+        <v>3.824038167815271</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.91263299937942</v>
+        <v>-2.68628292179697</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.204442945269018</v>
+        <v>2.294982976301998</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6130413448872029</v>
+        <v>0.7556342411562845</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.737677376266856</v>
+        <v>3.823233114028305</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.919541704879101</v>
+        <v>-2.693191627296651</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.214752869935065</v>
+        <v>2.305292900968045</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6130413448872029</v>
+        <v>0.7556342411562845</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.750750783132774</v>
+        <v>3.836306520894223</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.92110334769396</v>
+        <v>-2.69475327011151</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.214128212809121</v>
+        <v>2.304668243842101</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6130413448872029</v>
+        <v>0.7556342411562845</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.750750783132774</v>
+        <v>3.836306520894223</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.949004134803433</v>
+        <v>-2.722654057220983</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.201491939092334</v>
+        <v>2.292031970125314</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5784444207442681</v>
+        <v>0.7210373170133497</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.728516669774015</v>
+        <v>3.814072407535464</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.952037132316107</v>
+        <v>-2.725687054733657</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.197043184064463</v>
+        <v>2.287583215097443</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5754114232315941</v>
+        <v>0.7180043195006758</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.72346131524361</v>
+        <v>3.809017053005059</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.972098453592614</v>
+        <v>-2.745748376010164</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.255724615144364</v>
+        <v>2.346264646177344</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.555350101955087</v>
+        <v>0.6979429982241687</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.778130482068209</v>
+        <v>3.863686219829658</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.228819271587438</v>
+        <v>-3.002469194004988</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.293348006948281</v>
+        <v>2.383888037981261</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4469355278112722</v>
+        <v>0.5895284240803539</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.853393456583767</v>
+        <v>3.938949194345216</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.764553669187114</v>
+        <v>3.874272178266803</v>
       </c>
       <c r="C2017" t="n">
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.565237345893892</v>
+        <v>-3.337893641500801</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.22776104637134</v>
+        <v>2.318698528128576</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4469355278112722</v>
+        <v>0.5895284240803539</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.922373725729408</v>
+        <v>4.007929463490856</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-495.4%</t>
+          <t>-495.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.4%</t>
+          <t>-144.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-122.2%</t>
+          <t>-122.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-165.0%</t>
+          <t>-168.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-47.6%</t>
         </is>
       </c>
     </row>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.934779158359813</v>
+        <v>-6.936402590291633</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3132482271274224</v>
+        <v>0.3125988543546945</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.9143438712046807</v>
+        <v>-0.915818970131602</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.538909992062287</v>
+        <v>2.538024932706134</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.786839116952214</v>
+        <v>-6.788462548884033</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2525453210022945</v>
+        <v>0.2518959482295666</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8940229552961232</v>
+        <v>-0.8954980542230444</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.431223618919254</v>
+        <v>2.430338559563101</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.733869594698225</v>
+        <v>-6.735493026630045</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2650191436504117</v>
+        <v>0.2643697708776838</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8410534330421343</v>
+        <v>-0.8425285319690555</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.454291346018169</v>
+        <v>2.453406286662016</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.690321187927535</v>
+        <v>-6.691944619859354</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2754778942635947</v>
+        <v>0.2748285214908668</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8410534330421343</v>
+        <v>-0.8425285319690555</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.447330733923076</v>
+        <v>2.446445674566923</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.448172794473677</v>
+        <v>-6.449796226405496</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3867996060262811</v>
+        <v>0.3861502332535531</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8410534330421343</v>
+        <v>-0.8425285319690555</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.461793088304219</v>
+        <v>2.460908028948066</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.339913657351155</v>
+        <v>-6.341537089282975</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4246353813344848</v>
+        <v>0.4239860085617568</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8410534330421343</v>
+        <v>-0.8425285319690555</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.456325208763414</v>
+        <v>2.455440149407261</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.216622522534024</v>
+        <v>-6.218245954465844</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4714499292719139</v>
+        <v>0.470800556499186</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7177622982250038</v>
+        <v>-0.719237397151925</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.527797983664269</v>
+        <v>2.526912924308116</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.195473323630581</v>
+        <v>-6.1970967555624</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4876105870706162</v>
+        <v>0.4869612142978887</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6966130993215605</v>
+        <v>-0.6980881982484817</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.54818848124366</v>
+        <v>2.547303421887507</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.951707881647136</v>
+        <v>-5.953331313578956</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5808974722110447</v>
+        <v>0.5802480994383172</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6966130993215605</v>
+        <v>-0.6980881982484817</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.543969189590711</v>
+        <v>2.543084130234558</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.849945061369842</v>
+        <v>-5.851568493301661</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.623726914241979</v>
+        <v>0.6230775414692511</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6833940309291318</v>
+        <v>-0.684869129856053</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.554024944546184</v>
+        <v>2.553139885190031</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.600094667420767</v>
+        <v>-5.601718099352587</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7164091468053106</v>
+        <v>0.7157597740325832</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6833940309291318</v>
+        <v>-0.684869129856053</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.546767019529886</v>
+        <v>2.545881960173733</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.424202574953334</v>
+        <v>-5.425826006885154</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7903651073129327</v>
+        <v>0.7897157345402044</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6833940309291318</v>
+        <v>-0.684869129856053</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.550366143050535</v>
+        <v>2.549481083694382</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.252756111930871</v>
+        <v>-5.254379543862691</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8722711985764717</v>
+        <v>0.8716218258037438</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5119475679066686</v>
+        <v>-0.5134226668335898</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.666561526918566</v>
+        <v>2.665676467562414</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.178466546192531</v>
+        <v>-5.180089978124352</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9010075024881044</v>
+        <v>0.9003581297153764</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4376580021683293</v>
+        <v>-0.4391331010952506</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.710155743977867</v>
+        <v>2.709270684621714</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.114830803958597</v>
+        <v>-5.116454235890417</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9311566004359957</v>
+        <v>0.9305072276632673</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3740222599343948</v>
+        <v>-0.375497358861316</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.753031990372545</v>
+        <v>2.752146931016392</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.003404044632677</v>
+        <v>-5.005027476564497</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9569215629501593</v>
+        <v>0.9562721901774309</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3740222599343948</v>
+        <v>-0.375497358861316</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.73422624915634</v>
+        <v>2.733341189800188</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.762973547827817</v>
+        <v>-4.764596979759637</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.054836838296981</v>
+        <v>1.054187465524252</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1335917631295345</v>
+        <v>-0.1350668620564557</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.880227623864134</v>
+        <v>2.879342564507982</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.690730979656622</v>
+        <v>-4.692354411588442</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.087663179400279</v>
+        <v>1.087013806627551</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1335917631295345</v>
+        <v>-0.1350668620564557</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.884156937698954</v>
+        <v>2.883271878342802</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.637732657375234</v>
+        <v>-4.639356089307054</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.109541092230174</v>
+        <v>1.108891719457446</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.07825550412759569</v>
+        <v>-0.0797306030545169</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.918037277017458</v>
+        <v>2.917152217661305</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.528927771895507</v>
+        <v>-4.530551203827327</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.150061117642058</v>
+        <v>1.14941174486933</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.07825550412759569</v>
+        <v>-0.0797306030545169</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.915035348237451</v>
+        <v>2.914150288881298</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.308906973858496</v>
+        <v>-4.310530405790317</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.239648473867477</v>
+        <v>1.238999101094748</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06296434094038456</v>
+        <v>0.06148924201346334</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.001346292288853</v>
+        <v>3.000461232932701</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.176039284795219</v>
+        <v>-4.177662716727039</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.308689732294611</v>
+        <v>1.308040359521883</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.06296434094038456</v>
+        <v>0.06148924201346334</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.017240475090677</v>
+        <v>3.016355415734524</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.05586620143072</v>
+        <v>-4.057489633362541</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.357904810080712</v>
+        <v>1.357255437307984</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1831374243048835</v>
+        <v>0.1816623253779623</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.090490169549678</v>
+        <v>3.089605110193525</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.911194056330983</v>
+        <v>-3.912817488262803</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.425861770682047</v>
+        <v>1.425212397909319</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3278095694046209</v>
+        <v>0.3263344704776997</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.18738155917096</v>
+        <v>3.186496499814808</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.971068883688675</v>
+        <v>-3.972692315620495</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.387949331140396</v>
+        <v>1.387299958367668</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2679347420469288</v>
+        <v>0.2664596431200076</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.137494154157771</v>
+        <v>3.136609094801618</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.851248652777838</v>
+        <v>-3.852872084709658</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.451166592738939</v>
+        <v>1.450517219966211</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2679347420469288</v>
+        <v>0.2664596431200076</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.152783323391979</v>
+        <v>3.151898264035827</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.853718359239644</v>
+        <v>-3.855341791171464</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.357822909476659</v>
+        <v>1.357173536703931</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2654650355851226</v>
+        <v>0.2639899366582014</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.058945698837337</v>
+        <v>3.058060639481185</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.922088545563653</v>
+        <v>-3.923711977495474</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.249736696432356</v>
+        <v>1.249087323659628</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2747407346213376</v>
+        <v>0.2732656356944164</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.983772979744368</v>
+        <v>2.982887920388215</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.9358765984107</v>
+        <v>-3.93750003034252</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.234658183925429</v>
+        <v>1.234008811152701</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2747407346213376</v>
+        <v>0.2732656356944164</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.974209688376259</v>
+        <v>2.973324629020106</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.966869757739405</v>
+        <v>-3.968493189671226</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.046970485234334</v>
+        <v>1.046321112461605</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2747407346213376</v>
+        <v>0.2732656356944164</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.798919253416646</v>
+        <v>2.798034194060493</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.791395497946936</v>
+        <v>-3.793018929878757</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.121727421143109</v>
+        <v>1.121078048370381</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2747407346213376</v>
+        <v>0.2732656356944164</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.803486485408433</v>
+        <v>2.802601426052281</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.902331750588185</v>
+        <v>-3.903955182520005</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.053094948847817</v>
+        <v>1.052445576075088</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2747407346213376</v>
+        <v>0.2732656356944164</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.77922851416964</v>
+        <v>2.778343454813488</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.868668205115903</v>
+        <v>-3.870291637047723</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.069691752256635</v>
+        <v>1.069042379483907</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3084042800936194</v>
+        <v>0.3069291811666982</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.802558026672915</v>
+        <v>2.801672967316763</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.80881558591218</v>
+        <v>-3.810439017844</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.103805186370256</v>
+        <v>1.103155813597528</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3084042800936194</v>
+        <v>0.3069291811666982</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.812730413105048</v>
+        <v>2.811845353748895</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.722572122885802</v>
+        <v>-3.724195554817623</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.133248842154668</v>
+        <v>1.132599469381939</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3084042800936194</v>
+        <v>0.3069291811666982</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.807676683678908</v>
+        <v>2.806791624322755</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.767878942284782</v>
+        <v>-3.769502374216603</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.106901889839601</v>
+        <v>1.106252517066873</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2675941170843886</v>
+        <v>0.2661190181574674</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.774966361317895</v>
+        <v>2.774081301961742</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.796912046987084</v>
+        <v>-3.798535478918904</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.095840520991782</v>
+        <v>1.095191148219054</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2675941170843886</v>
+        <v>0.2661190181574674</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.775518234350996</v>
+        <v>2.774633174994844</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.704101565536225</v>
+        <v>-3.705724997468045</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.062237405463492</v>
+        <v>1.061588032690763</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.360404598535248</v>
+        <v>0.3589294996083268</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.760477215112878</v>
+        <v>2.759592155756725</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.748491034865652</v>
+        <v>-3.750114466797473</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.046355093656322</v>
+        <v>1.045705720883593</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3160151292058203</v>
+        <v>0.3145400302788991</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.735717009439822</v>
+        <v>2.734831950083669</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.635819816629402</v>
+        <v>-3.637443248561222</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.086499289462544</v>
+        <v>1.085849916689816</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4286863474420705</v>
+        <v>0.4272112485151493</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798395448893295</v>
+        <v>2.797510389537142</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.523442815446729</v>
+        <v>-3.52506624737855</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.136941385766281</v>
+        <v>1.136292012993553</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4286863474420705</v>
+        <v>0.4272112485151493</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.803886744723962</v>
+        <v>2.80300168536781</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.551223213348083</v>
+        <v>-3.552846645279903</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.137326428374279</v>
+        <v>1.13667705560155</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4009059495407175</v>
+        <v>0.3994308506137962</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.79871570775169</v>
+        <v>2.797830648395537</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.634224494373361</v>
+        <v>-3.635847926305182</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9424816359648203</v>
+        <v>0.9418322631920921</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3823350650135437</v>
+        <v>0.3808599660866225</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.625928897036038</v>
+        <v>2.625043837679886</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.742838572816693</v>
+        <v>-3.744462004748513</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.019185665306694</v>
+        <v>1.018536292533965</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3823350650135437</v>
+        <v>0.3808599660866225</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.746078557755244</v>
+        <v>2.745193498399091</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.70742953456855</v>
+        <v>-3.70905296650037</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.047862306708274</v>
+        <v>1.047212933935545</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3823350650135437</v>
+        <v>0.3808599660866225</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.760591583857567</v>
+        <v>2.759706524501414</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.669045872010399</v>
+        <v>-3.670669303942219</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.060635213073903</v>
+        <v>1.059985840301175</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4207187275716949</v>
+        <v>0.4192436286447737</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.781041222734827</v>
+        <v>2.780156163378674</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.491929541975233</v>
+        <v>-3.493552973907053</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.128210773933271</v>
+        <v>1.127561401160543</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4207187275716949</v>
+        <v>0.4192436286447737</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.777770251580129</v>
+        <v>2.776885192223976</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.537021786808778</v>
+        <v>-3.538645218740599</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.110857267761766</v>
+        <v>1.110207894989038</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3588226844023051</v>
+        <v>0.3573475854753839</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.741316017440408</v>
+        <v>2.740430958084255</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.357646365570011</v>
+        <v>-3.359269797501831</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.176394411563688</v>
+        <v>1.17574503879096</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5155994425730237</v>
+        <v>0.5141243436461025</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.829169047649254</v>
+        <v>2.828283988293101</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.402660579090617</v>
+        <v>-3.404284011022437</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.139196181487035</v>
+        <v>1.138546808714307</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4852505472584191</v>
+        <v>0.4837754483314979</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.791767165792081</v>
+        <v>2.790882106435928</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.669665089363052</v>
+        <v>-3.671288521294873</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.038085939717007</v>
+        <v>1.037436566944278</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2908875092154705</v>
+        <v>0.2894124102885493</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.680840905305257</v>
+        <v>2.679955845949105</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.770862870800225</v>
+        <v>-3.772486302732045</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9968107490386389</v>
+        <v>0.9961613762659107</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2224786956701513</v>
+        <v>0.2210035967432301</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.638999539074567</v>
+        <v>2.638114479718415</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.764351904185912</v>
+        <v>-3.765975336117733</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9970150972386806</v>
+        <v>0.9963657244659525</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2224786956701513</v>
+        <v>0.2210035967432301</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.636599500628884</v>
+        <v>2.635714441272731</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.745313776478615</v>
+        <v>-3.746937208410436</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.001155067529845</v>
+        <v>1.000505694757116</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1642950843389568</v>
+        <v>0.1628199854120356</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.598214053038412</v>
+        <v>2.597328993682259</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.776440407629233</v>
+        <v>-3.778063839561054</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.166286284008278</v>
+        <v>1.16563691123555</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1642950843389568</v>
+        <v>0.1628199854120356</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.775795921977093</v>
+        <v>2.77491086262094</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.79030716896315</v>
+        <v>-3.791930600894971</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.161572908460844</v>
+        <v>1.160923535688116</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1264371676051338</v>
+        <v>0.1249620686782126</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.753914500922932</v>
+        <v>2.75302944156678</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.745502997423221</v>
+        <v>-3.747126429355041</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.185503107473742</v>
+        <v>1.184853734701014</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1264371676051338</v>
+        <v>0.1249620686782126</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.759923031319858</v>
+        <v>2.759037971963706</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.597760027188218</v>
+        <v>-3.599383459120039</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.323752943359765</v>
+        <v>1.323103570587037</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.294244524840017</v>
+        <v>0.2927694259130958</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.93976009345281</v>
+        <v>2.938875034096657</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.699774709719439</v>
+        <v>-3.70139814165126</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.285740691878758</v>
+        <v>1.28509131910603</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.294244524840017</v>
+        <v>0.2927694259130958</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.942553714984291</v>
+        <v>2.941668655628138</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.693622003666655</v>
+        <v>-3.695245435598475</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.28886412269153</v>
+        <v>1.288214749918802</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3003972308928013</v>
+        <v>0.2989221319658801</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.94690768700762</v>
+        <v>2.946022627651467</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.710431301817156</v>
+        <v>-3.712054733748977</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.28122088017144</v>
+        <v>1.280571507398711</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2835879327422997</v>
+        <v>0.2821128338153784</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.93590258485743</v>
+        <v>2.935017525501276</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.648133303041035</v>
+        <v>-3.649756734972855</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.372475633478709</v>
+        <v>1.371826260705981</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2835879327422997</v>
+        <v>0.2821128338153784</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.00223813865425</v>
+        <v>3.001353079298098</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.540666251398268</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.446343105375877</v>
+        <v>-3.447966537307697</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.16177258493417</v>
+        <v>1.161123212161442</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.481606124911454</v>
+        <v>0.4801310259845328</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.829629926345141</v>
+        <v>2.828744866988988</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.610956483720444</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.37296500828714</v>
+        <v>-3.374588440218961</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.26141405609184</v>
+        <v>1.260764683319112</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5549842220001906</v>
+        <v>0.5535091230732694</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.943947016920558</v>
+        <v>2.943061957564405</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.625584219836487</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.470705552912114</v>
+        <v>-3.472328984843935</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.236945574357894</v>
+        <v>1.236296201585166</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5390949438672104</v>
+        <v>0.5376198449402891</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.949041186156814</v>
+        <v>2.948156126800661</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.624120200661159</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.647043313035044</v>
+        <v>-3.648666744966864</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.164946451133394</v>
+        <v>1.164297078360666</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.362757183744281</v>
+        <v>0.3612820848173597</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.841774510907728</v>
+        <v>2.840889451551575</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.622611818701087</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.570621266603117</v>
+        <v>-3.572244698534937</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.194006887746093</v>
+        <v>1.193357514973365</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.362757183744281</v>
+        <v>0.3612820848173597</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.840266128947656</v>
+        <v>2.839381069591504</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.622474686136524</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.526248134964548</v>
+        <v>-3.527871566896369</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.211619007836957</v>
+        <v>1.210969635064229</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4071303153828496</v>
+        <v>0.4056552164559283</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.866752875366234</v>
+        <v>2.865867816010081</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.616868480275114</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.403413914077381</v>
+        <v>-3.405037346009201</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.255146490330414</v>
+        <v>1.254497117557686</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4071303153828496</v>
+        <v>0.4056552164559283</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.861146669504824</v>
+        <v>2.860261610148672</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.623250237302918</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.355758183516325</v>
+        <v>-3.357381615448146</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.280590539582641</v>
+        <v>1.279941166809913</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4547860459439052</v>
+        <v>0.453310947016984</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.896121864869261</v>
+        <v>2.895236805513109</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.628142610677643</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.255240025017571</v>
+        <v>-3.256863456949391</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.325690176356868</v>
+        <v>1.325040803584139</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5553042044426597</v>
+        <v>0.5538291055157385</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.961325133343239</v>
+        <v>2.960440073987086</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.614897283153515</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.31590661541996</v>
+        <v>-3.31753004735178</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.288178212671784</v>
+        <v>1.287528839899056</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.473605887724126</v>
+        <v>0.4721307887972048</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.899060815787991</v>
+        <v>2.898175756431839</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.618994985764144</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.271068213811562</v>
+        <v>-3.272691645743382</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.310211275925772</v>
+        <v>1.309561903153044</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4781493206689955</v>
+        <v>0.4766742217420743</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.905884578165542</v>
+        <v>2.904999518809389</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
         <v>2.623155925395222</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.37182684956856</v>
+        <v>-3.373450281500381</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.27406876125405</v>
+        <v>1.273419388481322</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3893237519419901</v>
+        <v>0.3878486530150689</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.856750176560416</v>
+        <v>2.855865117204264</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405955</v>
       </c>
       <c r="C1983" t="n">
         <v>2.629035527923059</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.32762401248266</v>
+        <v>-3.32924744441448</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.297629498616248</v>
+        <v>1.29698012584352</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4335265890278905</v>
+        <v>0.4320514901009693</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.889151481339794</v>
+        <v>2.888266421983641</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.186237397189293</v>
+        <v>-3.366226472077924</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.352594145202842</v>
+        <v>1.28059851524739</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5077763552434059</v>
+        <v>0.4690253918922999</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.93211134153835</v>
+        <v>2.908860763527687</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.206295476054133</v>
+        <v>-3.386284550942764</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.395818678839946</v>
+        <v>1.323823048884494</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5077763552434059</v>
+        <v>0.4690253918922999</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.98335910672139</v>
+        <v>2.960108528710726</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.166364802876243</v>
+        <v>-3.346353877764873</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.410231652705355</v>
+        <v>1.338236022749903</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5477070284212963</v>
+        <v>0.5089560650701902</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.005758215222377</v>
+        <v>2.982507637211714</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475134</v>
       </c>
       <c r="C1987" t="n">
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.115332710153714</v>
+        <v>-3.295321785042345</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.425592718032636</v>
+        <v>1.353597088077184</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5987391211438242</v>
+        <v>0.5599881577927182</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.031325699094164</v>
+        <v>3.0080751210835</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.050108529026509</v>
+        <v>-3.23009760391514</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.468869794576224</v>
+        <v>1.396874164620771</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6639633022710298</v>
+        <v>0.6252123389199238</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.087647611863193</v>
+        <v>3.064397033852529</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.012681508955375</v>
+        <v>-3.192670583844006</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.479801574903957</v>
+        <v>1.407805944948505</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6692148403002115</v>
+        <v>0.6304638769491054</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.086759506979982</v>
+        <v>3.063508928969318</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.032793164990083</v>
+        <v>-3.212782239878714</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.473013704821315</v>
+        <v>1.401018074865862</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6802421852976307</v>
+        <v>0.6414912219465246</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.094632706309674</v>
+        <v>3.07138212829901</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.979048350562878</v>
+        <v>-3.15903742545151</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.655069401613407</v>
+        <v>1.583073771657955</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6903054947380927</v>
+        <v>0.6515545313869866</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.261228462995162</v>
+        <v>3.237977884984498</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.955256781956736</v>
+        <v>-3.135245856845367</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.784698938273681</v>
+        <v>1.712703308318229</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.714097063344235</v>
+        <v>0.6753460999931289</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.395616313376664</v>
+        <v>3.372365735366</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.929172697692928</v>
+        <v>-3.109161772581559</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.786840547993063</v>
+        <v>1.714844918037611</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.714097063344235</v>
+        <v>0.6753460999931289</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.387324289390523</v>
+        <v>3.364073711379859</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.851041516843981</v>
+        <v>-3.031030591732613</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.816286215916422</v>
+        <v>1.744290585960969</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7882738742279195</v>
+        <v>0.7495229108768134</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.430023571504513</v>
+        <v>3.40677299349385</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.842149055450698</v>
+        <v>-3.02213813033933</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.837397606200526</v>
+        <v>1.765401976245074</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7882738742279195</v>
+        <v>0.7495229108768134</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.447577977231305</v>
+        <v>3.424327399220641</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.010625172420576</v>
+        <v>-3.190614247309207</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.761862206817159</v>
+        <v>1.689866576861706</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7603260385113387</v>
+        <v>0.7215750751602327</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.42266432320594</v>
+        <v>3.399413745195277</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.312825643558993</v>
+        <v>-2.492814718447624</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.022251715549654</v>
+        <v>1.950256085594201</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.689977979140928</v>
+        <v>0.6512270157898219</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.361725184771556</v>
+        <v>3.338474606760892</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.29010453987584</v>
+        <v>-2.470093614764472</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.02200417951982</v>
+        <v>1.950008549564367</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.689977979140928</v>
+        <v>0.6512270157898219</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.35238920726846</v>
+        <v>3.329138629257796</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.288379496585796</v>
+        <v>-2.468368571474428</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.181600322687006</v>
+        <v>2.109604692731554</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6917030224309717</v>
+        <v>0.6529520590798656</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.512330359093656</v>
+        <v>3.489079781082992</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.443160503364052</v>
+        <v>-2.623149578252683</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.156765742469351</v>
+        <v>2.084770112513898</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6583353483764955</v>
+        <v>0.6195843850253895</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.529387577154616</v>
+        <v>3.506136999143953</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.391725169979392</v>
+        <v>-2.571714244868023</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.17401523181276</v>
+        <v>2.102019601857307</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7097706817611552</v>
+        <v>0.6710197184100491</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.556924133174957</v>
+        <v>3.533673555164293</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.364773945652904</v>
+        <v>-2.544763020541535</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.194801875188097</v>
+        <v>2.122806245232644</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7246510277888744</v>
+        <v>0.6859000644377683</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.57585849443633</v>
+        <v>3.552607916425667</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.50072695370922</v>
+        <v>-2.680716028597852</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.32452380411053</v>
+        <v>2.252528174155077</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7246510277888744</v>
+        <v>0.6859000644377683</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.75996162658129</v>
+        <v>3.736711048570626</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.523135071514092</v>
+        <v>-2.703124146402724</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.307677251891574</v>
+        <v>2.235681621936122</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7246510277888744</v>
+        <v>0.6859000644377683</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.752078321484283</v>
+        <v>3.728827743473619</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.671140838993492</v>
+        <v>-2.851129913882123</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.250528944449452</v>
+        <v>2.178533314494</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6379240189253329</v>
+        <v>0.5991730555742268</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.702096115715796</v>
+        <v>3.678845537705132</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.680581764882022</v>
+        <v>-2.860570839770653</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.303006291815887</v>
+        <v>2.231010661860434</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7603511364687243</v>
+        <v>0.7216001731176183</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.831806103963678</v>
+        <v>3.808555525953014</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.679295001342465</v>
+        <v>-2.859284076231097</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.30641209177701</v>
+        <v>2.234416461821558</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7616379000082809</v>
+        <v>0.7228869366571749</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.835469256632713</v>
+        <v>3.812218678622049</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.680852055331757</v>
+        <v>-2.860841130220388</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.303901083075069</v>
+        <v>2.231905453119617</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7616379000082809</v>
+        <v>0.7228869366571749</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.833581069526488</v>
+        <v>3.810330491515824</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.688123940855221</v>
+        <v>-2.868113015743853</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.295812558468546</v>
+        <v>2.223816928513093</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7543660144848161</v>
+        <v>0.71561505113371</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.824038167815271</v>
+        <v>3.800787589804608</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.68628292179697</v>
+        <v>-2.866271996685601</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.294982976301998</v>
+        <v>2.222987346346546</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7556342411562845</v>
+        <v>0.7168832778051785</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.823233114028305</v>
+        <v>3.799982536017641</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.693191627296651</v>
+        <v>-2.873180702185282</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.305292900968045</v>
+        <v>2.233297271012592</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7556342411562845</v>
+        <v>0.7168832778051785</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.836306520894223</v>
+        <v>3.81305594288356</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.69475327011151</v>
+        <v>-2.874742345000142</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.304668243842101</v>
+        <v>2.232672613886648</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7556342411562845</v>
+        <v>0.7168832778051785</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.836306520894223</v>
+        <v>3.81305594288356</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.722654057220983</v>
+        <v>-2.902643132109615</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.292031970125314</v>
+        <v>2.220036340169861</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7210373170133497</v>
+        <v>0.6822863536622437</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.814072407535464</v>
+        <v>3.790821829524801</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.725687054733657</v>
+        <v>-2.905676129622289</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.287583215097443</v>
+        <v>2.21558758514199</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7180043195006758</v>
+        <v>0.6792533561495697</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.809017053005059</v>
+        <v>3.785766474994395</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.745748376010164</v>
+        <v>-2.925737450898795</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.346264646177344</v>
+        <v>2.274269016221891</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6979429982241687</v>
+        <v>0.6591920348730627</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.863686219829658</v>
+        <v>3.840435641818995</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.002469194004988</v>
+        <v>-3.182458268893619</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.383888037981261</v>
+        <v>2.311892408025809</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5895284240803539</v>
+        <v>0.5507774607292478</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.938949194345216</v>
+        <v>3.915698616334553</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.874272178266803</v>
+        <v>3.874272178266801</v>
       </c>
       <c r="C2017" t="n">
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.337893641500801</v>
+        <v>-3.33644468666976</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.318698528128576</v>
+        <v>2.319278110060992</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5895284240803539</v>
+        <v>0.5507774607292478</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.007929463490856</v>
+        <v>3.984678885480193</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-66.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>461.0%</t>
+          <t>461.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-495.2%</t>
+          <t>-476.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.3%</t>
+          <t>-136.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-122.9%</t>
+          <t>-122.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.9%</t>
+          <t>-164.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-53.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2017"/>
+  <dimension ref="A1:G2018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.936402590291633</v>
+        <v>-6.927171457262393</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3125988543546945</v>
+        <v>0.3162913075663902</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.915818970131602</v>
+        <v>-0.9102463741854541</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.538024932706134</v>
+        <v>2.541368490273823</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.788462548884033</v>
+        <v>-6.779231415854793</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2518959482295666</v>
+        <v>0.2555884014412624</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8954980542230444</v>
+        <v>-0.8899254582768965</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.430338559563101</v>
+        <v>2.43368211713079</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.735493026630045</v>
+        <v>-6.726261893600805</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2643697708776838</v>
+        <v>0.2680622240893795</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8425285319690555</v>
+        <v>-0.8369559360229076</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.453406286662016</v>
+        <v>2.456749844229705</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.691944619859354</v>
+        <v>-6.682713486830115</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2748285214908668</v>
+        <v>0.2785209747025625</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8425285319690555</v>
+        <v>-0.8369559360229076</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.446445674566923</v>
+        <v>2.449789232134612</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.449796226405496</v>
+        <v>-6.440565093376256</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3861502332535531</v>
+        <v>0.3898426864652489</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8425285319690555</v>
+        <v>-0.8369559360229076</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.460908028948066</v>
+        <v>2.464251586515755</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.341537089282975</v>
+        <v>-6.332305956253735</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4239860085617568</v>
+        <v>0.4276784617734526</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8425285319690555</v>
+        <v>-0.8369559360229076</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.455440149407261</v>
+        <v>2.45878370697495</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.218245954465844</v>
+        <v>-6.209014821436604</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.470800556499186</v>
+        <v>0.4744930097108822</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.719237397151925</v>
+        <v>-0.7136648012057771</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.526912924308116</v>
+        <v>2.530256481875805</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.1970967555624</v>
+        <v>-6.187865622533161</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4869612142978887</v>
+        <v>0.4906536675095845</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6980881982484817</v>
+        <v>-0.6925156023023338</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.547303421887507</v>
+        <v>2.550646979455196</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.953331313578956</v>
+        <v>-5.944100180549716</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5802480994383172</v>
+        <v>0.583940552650013</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6980881982484817</v>
+        <v>-0.6925156023023338</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.543084130234558</v>
+        <v>2.546427687802247</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.851568493301661</v>
+        <v>-5.842337360272421</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6230775414692511</v>
+        <v>0.6267699946809469</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.684869129856053</v>
+        <v>-0.6792965339099051</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.553139885190031</v>
+        <v>2.55648344275772</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.601718099352587</v>
+        <v>-5.592486966323347</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7157597740325832</v>
+        <v>0.7194522272442789</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.684869129856053</v>
+        <v>-0.6792965339099051</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.545881960173733</v>
+        <v>2.549225517741422</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.425826006885154</v>
+        <v>-5.416594873855914</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7897157345402044</v>
+        <v>0.793408187751901</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.684869129856053</v>
+        <v>-0.6792965339099051</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.549481083694382</v>
+        <v>2.552824641262071</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.254379543862691</v>
+        <v>-5.24514841083345</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8716218258037438</v>
+        <v>0.87531427901544</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5134226668335898</v>
+        <v>-0.5078500708874419</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.665676467562414</v>
+        <v>2.669020025130103</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.180089978124352</v>
+        <v>-5.170858845095111</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9003581297153764</v>
+        <v>0.9040505829270726</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4391331010952506</v>
+        <v>-0.4335605051491027</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.709270684621714</v>
+        <v>2.712614242189403</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.116454235890417</v>
+        <v>-5.107223102861177</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9305072276632673</v>
+        <v>0.9341996808749635</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.375497358861316</v>
+        <v>-0.3699247629151681</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.752146931016392</v>
+        <v>2.755490488584081</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.005027476564497</v>
+        <v>-4.995796343535257</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9562721901774309</v>
+        <v>0.9599646433891273</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.375497358861316</v>
+        <v>-0.3699247629151681</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.733341189800188</v>
+        <v>2.736684747367877</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.764596979759637</v>
+        <v>-4.755365846730396</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.054187465524252</v>
+        <v>1.057879918735949</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1350668620564557</v>
+        <v>-0.1294942661103078</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.879342564507982</v>
+        <v>2.88268612207567</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.692354411588442</v>
+        <v>-4.683123278559202</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.087013806627551</v>
+        <v>1.090706259839247</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1350668620564557</v>
+        <v>-0.1294942661103078</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.883271878342802</v>
+        <v>2.88661543591049</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.639356089307054</v>
+        <v>-4.630124956277814</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.108891719457446</v>
+        <v>1.112584172669142</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.0797306030545169</v>
+        <v>-0.07415800710836901</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.917152217661305</v>
+        <v>2.920495775228994</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.530551203827327</v>
+        <v>-4.521320070798087</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.14941174486933</v>
+        <v>1.153104198081026</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.0797306030545169</v>
+        <v>-0.07415800710836901</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.914150288881298</v>
+        <v>2.917493846448987</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.310530405790317</v>
+        <v>-4.301299272761076</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.238999101094748</v>
+        <v>1.242691554306445</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06148924201346334</v>
+        <v>0.06706183795961124</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.000461232932701</v>
+        <v>3.003804790500389</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.177662716727039</v>
+        <v>-4.168431583697799</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.308040359521883</v>
+        <v>1.311732812733579</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.06148924201346334</v>
+        <v>0.06706183795961124</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.016355415734524</v>
+        <v>3.019698973302213</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.057489633362541</v>
+        <v>-4.0482585003333</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.357255437307984</v>
+        <v>1.36094789051968</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1816623253779623</v>
+        <v>0.1872349213241102</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.089605110193525</v>
+        <v>3.092948667761214</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.912817488262803</v>
+        <v>-3.903586355233562</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.425212397909319</v>
+        <v>1.428904851121015</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3263344704776997</v>
+        <v>0.3319070664238476</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.186496499814808</v>
+        <v>3.189840057382496</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.972692315620495</v>
+        <v>-3.963461182591255</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.387299958367668</v>
+        <v>1.390992411579364</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2664596431200076</v>
+        <v>0.2720322390661555</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.136609094801618</v>
+        <v>3.139952652369307</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.852872084709658</v>
+        <v>-3.843640951680417</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.450517219966211</v>
+        <v>1.454209673177908</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2664596431200076</v>
+        <v>0.2720322390661555</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.151898264035827</v>
+        <v>3.155241821603515</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.855341791171464</v>
+        <v>-3.846110658142223</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.357173536703931</v>
+        <v>1.360865989915627</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2639899366582014</v>
+        <v>0.2695625326043493</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.058060639481185</v>
+        <v>3.061404197048873</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.923711977495474</v>
+        <v>-3.914480844466233</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.249087323659628</v>
+        <v>1.252779776871324</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2732656356944164</v>
+        <v>0.2788382316405643</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.982887920388215</v>
+        <v>2.986231477955904</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.93750003034252</v>
+        <v>-3.92826889731328</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.234008811152701</v>
+        <v>1.237701264364397</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2732656356944164</v>
+        <v>0.2788382316405643</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.973324629020106</v>
+        <v>2.976668186587795</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.968493189671226</v>
+        <v>-3.959262056641985</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.046321112461605</v>
+        <v>1.050013565673302</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2732656356944164</v>
+        <v>0.2788382316405643</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.798034194060493</v>
+        <v>2.801377751628182</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.793018929878757</v>
+        <v>-3.783787796849516</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.121078048370381</v>
+        <v>1.124770501582077</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2732656356944164</v>
+        <v>0.2788382316405643</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.802601426052281</v>
+        <v>2.80594498361997</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.903955182520005</v>
+        <v>-3.894724049490764</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.052445576075088</v>
+        <v>1.056138029286785</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2732656356944164</v>
+        <v>0.2788382316405643</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.778343454813488</v>
+        <v>2.781687012381177</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.870291637047723</v>
+        <v>-3.861060504018483</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.069042379483907</v>
+        <v>1.072734832695603</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3069291811666982</v>
+        <v>0.3125017771128461</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.801672967316763</v>
+        <v>2.805016524884451</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.810439017844</v>
+        <v>-3.801207884814759</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.103155813597528</v>
+        <v>1.106848266809225</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3069291811666982</v>
+        <v>0.3125017771128461</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.811845353748895</v>
+        <v>2.815188911316584</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.724195554817623</v>
+        <v>-3.714964421788382</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.132599469381939</v>
+        <v>1.136291922593636</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3069291811666982</v>
+        <v>0.3125017771128461</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.806791624322755</v>
+        <v>2.810135181890444</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.769502374216603</v>
+        <v>-3.760271241187362</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.106252517066873</v>
+        <v>1.10994497027857</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2661190181574674</v>
+        <v>0.2716916141036153</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.774081301961742</v>
+        <v>2.777424859529431</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.798535478918904</v>
+        <v>-3.789304345889664</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.095191148219054</v>
+        <v>1.09888360143075</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2661190181574674</v>
+        <v>0.2716916141036153</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.774633174994844</v>
+        <v>2.777976732562533</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.705724997468045</v>
+        <v>-3.696493864438804</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.061588032690763</v>
+        <v>1.06528048590246</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3589294996083268</v>
+        <v>0.3645020955544747</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.759592155756725</v>
+        <v>2.762935713324414</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.750114466797473</v>
+        <v>-3.740883333768232</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.045705720883593</v>
+        <v>1.04939817409529</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3145400302788991</v>
+        <v>0.320112626225047</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.734831950083669</v>
+        <v>2.738175507651358</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.637443248561222</v>
+        <v>-3.628212115531982</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.085849916689816</v>
+        <v>1.089542369901513</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4272112485151493</v>
+        <v>0.4327838444612972</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.797510389537142</v>
+        <v>2.800853947104831</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.52506624737855</v>
+        <v>-3.515835114349309</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.136292012993553</v>
+        <v>1.139984466205249</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4272112485151493</v>
+        <v>0.4327838444612972</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.80300168536781</v>
+        <v>2.806345242935498</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.552846645279903</v>
+        <v>-3.543615512250662</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.13667705560155</v>
+        <v>1.140369508813247</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3994308506137962</v>
+        <v>0.4050034465599441</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.797830648395537</v>
+        <v>2.801174205963226</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.635847926305182</v>
+        <v>-3.626616793275941</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9418322631920921</v>
+        <v>0.9455247164037883</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3808599660866225</v>
+        <v>0.3864325620327704</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.625043837679886</v>
+        <v>2.628387395247575</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.744462004748513</v>
+        <v>-3.735230871719272</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.018536292533965</v>
+        <v>1.022228745745662</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3808599660866225</v>
+        <v>0.3864325620327704</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.745193498399091</v>
+        <v>2.74853705596678</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.70905296650037</v>
+        <v>-3.699821833471129</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.047212933935545</v>
+        <v>1.050905387147242</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3808599660866225</v>
+        <v>0.3864325620327704</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.759706524501414</v>
+        <v>2.763050082069103</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.670669303942219</v>
+        <v>-3.661438170912978</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.059985840301175</v>
+        <v>1.063678293512871</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4192436286447737</v>
+        <v>0.4248162245909216</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.780156163378674</v>
+        <v>2.783499720946363</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.493552973907053</v>
+        <v>-3.484321840877812</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.127561401160543</v>
+        <v>1.13125385437224</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4192436286447737</v>
+        <v>0.4248162245909216</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.776885192223976</v>
+        <v>2.780228749791665</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.538645218740599</v>
+        <v>-3.529414085711358</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.110207894989038</v>
+        <v>1.113900348200734</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3573475854753839</v>
+        <v>0.3629201814215318</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.740430958084255</v>
+        <v>2.743774515651944</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.359269797501831</v>
+        <v>-3.35003866447259</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.17574503879096</v>
+        <v>1.179437492002656</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5141243436461025</v>
+        <v>0.5196969395922504</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.828283988293101</v>
+        <v>2.83162754586079</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.404284011022437</v>
+        <v>-3.395052877993197</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.138546808714307</v>
+        <v>1.142239261926003</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4837754483314979</v>
+        <v>0.4893480442776458</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.790882106435928</v>
+        <v>2.794225664003616</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.671288521294873</v>
+        <v>-3.662057388265632</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.037436566944278</v>
+        <v>1.041129020155975</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2894124102885493</v>
+        <v>0.2949850062346972</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.679955845949105</v>
+        <v>2.683299403516793</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.772486302732045</v>
+        <v>-3.763255169702805</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9961613762659107</v>
+        <v>0.9998538294776069</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2210035967432301</v>
+        <v>0.226576192689378</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.638114479718415</v>
+        <v>2.641458037286103</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.765975336117733</v>
+        <v>-3.756744203088492</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9963657244659525</v>
+        <v>1.000058177677649</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2210035967432301</v>
+        <v>0.226576192689378</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.635714441272731</v>
+        <v>2.63905799884042</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.746937208410436</v>
+        <v>-3.737706075381195</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.000505694757116</v>
+        <v>1.004198147968813</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1628199854120356</v>
+        <v>0.1683925813581835</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.597328993682259</v>
+        <v>2.600672551249948</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.778063839561054</v>
+        <v>-3.768832706531813</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.16563691123555</v>
+        <v>1.169329364447246</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1628199854120356</v>
+        <v>0.1683925813581835</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.77491086262094</v>
+        <v>2.778254420188629</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.791930600894971</v>
+        <v>-3.78269946786573</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.160923535688116</v>
+        <v>1.164615988899813</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1249620686782126</v>
+        <v>0.1305346646243605</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75302944156678</v>
+        <v>2.756372999134468</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.747126429355041</v>
+        <v>-3.7378952963258</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.184853734701014</v>
+        <v>1.18854618791271</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1249620686782126</v>
+        <v>0.1305346646243605</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.759037971963706</v>
+        <v>2.762381529531394</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.599383459120039</v>
+        <v>-3.590152326090798</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.323103570587037</v>
+        <v>1.326796023798733</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2927694259130958</v>
+        <v>0.2983420218592437</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.938875034096657</v>
+        <v>2.942218591664346</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.70139814165126</v>
+        <v>-3.692167008622019</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.28509131910603</v>
+        <v>1.288783772317726</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2927694259130958</v>
+        <v>0.2983420218592437</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.941668655628138</v>
+        <v>2.945012213195827</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.695245435598475</v>
+        <v>-3.686014302569235</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.288214749918802</v>
+        <v>1.291907203130498</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2989221319658801</v>
+        <v>0.304494727912028</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.946022627651467</v>
+        <v>2.949366185219156</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.712054733748977</v>
+        <v>-3.702823600719736</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.280571507398711</v>
+        <v>1.284263960610408</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2821128338153784</v>
+        <v>0.2876854297615263</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.935017525501276</v>
+        <v>2.938361083068965</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.649756734972855</v>
+        <v>-3.640525601943614</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.371826260705981</v>
+        <v>1.375518713917677</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2821128338153784</v>
+        <v>0.2876854297615263</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.001353079298098</v>
+        <v>3.004696636865786</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.540666251398268</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.447966537307697</v>
+        <v>-3.438735404278456</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.161123212161442</v>
+        <v>1.164815665373139</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4801310259845328</v>
+        <v>0.4857036219306807</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.828744866988988</v>
+        <v>2.832088424556677</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.610956483720444</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.374588440218961</v>
+        <v>-3.36535730718972</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.260764683319112</v>
+        <v>1.264457136530808</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5535091230732694</v>
+        <v>0.5590817190194173</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.943061957564405</v>
+        <v>2.946405515132094</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.625584219836487</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.472328984843935</v>
+        <v>-3.463097851814694</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.236296201585166</v>
+        <v>1.239988654796862</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5376198449402891</v>
+        <v>0.543192440886437</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.948156126800661</v>
+        <v>2.95149968436835</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.624120200661159</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.648666744966864</v>
+        <v>-3.639435611937623</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.164297078360666</v>
+        <v>1.167989531572362</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3612820848173597</v>
+        <v>0.3668546807635076</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.840889451551575</v>
+        <v>2.844233009119264</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.622611818701087</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.572244698534937</v>
+        <v>-3.563013565505697</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.193357514973365</v>
+        <v>1.197049968185061</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3612820848173597</v>
+        <v>0.3668546807635076</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.839381069591504</v>
+        <v>2.842724627159192</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.622474686136524</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.527871566896369</v>
+        <v>-3.518640433867128</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.210969635064229</v>
+        <v>1.214662088275925</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4056552164559283</v>
+        <v>0.4112278124020762</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.865867816010081</v>
+        <v>2.86921137357777</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.616868480275114</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.405037346009201</v>
+        <v>-3.395806212979961</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.254497117557686</v>
+        <v>1.258189570769383</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4056552164559283</v>
+        <v>0.4112278124020762</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.860261610148672</v>
+        <v>2.86360516771636</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.623250237302918</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.357381615448146</v>
+        <v>-3.348150482418905</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.279941166809913</v>
+        <v>1.283633620021609</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.453310947016984</v>
+        <v>0.4588835429631319</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.895236805513109</v>
+        <v>2.898580363080798</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.628142610677643</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.256863456949391</v>
+        <v>-3.247632323920151</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.325040803584139</v>
+        <v>1.328733256795836</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5538291055157385</v>
+        <v>0.5594017014618864</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.960440073987086</v>
+        <v>2.963783631554775</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.614897283153515</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.31753004735178</v>
+        <v>-3.30829891432254</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.287528839899056</v>
+        <v>1.291221293110752</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4721307887972048</v>
+        <v>0.4777033847433527</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.898175756431839</v>
+        <v>2.901519313999527</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.618994985764144</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.272691645743382</v>
+        <v>-3.263460512714142</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.309561903153044</v>
+        <v>1.31325435636474</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4766742217420743</v>
+        <v>0.4822468176882222</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.904999518809389</v>
+        <v>2.908343076377077</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.623155925395222</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.373450281500381</v>
+        <v>-3.36421914847114</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.273419388481322</v>
+        <v>1.277111841693019</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3878486530150689</v>
+        <v>0.3934212489612168</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.855865117204264</v>
+        <v>2.859208674771952</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.629035527923059</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.32924744441448</v>
+        <v>-3.32001631138524</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.29698012584352</v>
+        <v>1.300672579055216</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4320514901009693</v>
+        <v>0.4376240860471172</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.888266421983641</v>
+        <v>2.89160997955133</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.366226472077924</v>
+        <v>-3.178629696091873</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.28059851524739</v>
+        <v>1.35563722564181</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4690253918922999</v>
+        <v>0.5118738522626326</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.908860763527687</v>
+        <v>2.934569839749886</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.386284550942764</v>
+        <v>-3.198687774956713</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.323823048884494</v>
+        <v>1.398861759278914</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4690253918922999</v>
+        <v>0.5118738522626326</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.960108528710726</v>
+        <v>2.985817604932926</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.346353877764873</v>
+        <v>-3.158757101778822</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.338236022749903</v>
+        <v>1.413274733144323</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5089560650701902</v>
+        <v>0.5518045254405229</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.982507637211714</v>
+        <v>3.008216713433913</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.295321785042345</v>
+        <v>-3.107725009056294</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.353597088077184</v>
+        <v>1.428635798471604</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5599881577927182</v>
+        <v>0.6028366181630509</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.0080751210835</v>
+        <v>3.0337841973057</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.23009760391514</v>
+        <v>-3.042500827929088</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.396874164620771</v>
+        <v>1.471912875015192</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6252123389199238</v>
+        <v>0.6680607992902565</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.064397033852529</v>
+        <v>3.090106110074728</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.192670583844006</v>
+        <v>-3.005073807857955</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.407805944948505</v>
+        <v>1.482844655342926</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6304638769491054</v>
+        <v>0.6733123373194382</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.063508928969318</v>
+        <v>3.089218005191518</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.212782239878714</v>
+        <v>-3.025185463892663</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.401018074865862</v>
+        <v>1.476056785260283</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6414912219465246</v>
+        <v>0.6843396823168574</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.07138212829901</v>
+        <v>3.09709120452121</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.15903742545151</v>
+        <v>-2.971440649465458</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.583073771657955</v>
+        <v>1.658112482052375</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6515545313869866</v>
+        <v>0.6944029917573193</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.237977884984498</v>
+        <v>3.263686961206698</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.135245856845367</v>
+        <v>-2.947649080859316</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.712703308318229</v>
+        <v>1.787742018712649</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.6753460999931289</v>
+        <v>0.7181945603634616</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.372365735366</v>
+        <v>3.3980748115882</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.109161772581559</v>
+        <v>-2.921564996595508</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.714844918037611</v>
+        <v>1.789883628432032</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.6753460999931289</v>
+        <v>0.7181945603634616</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.364073711379859</v>
+        <v>3.389782787602059</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.031030591732613</v>
+        <v>-2.843433815746561</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.744290585960969</v>
+        <v>1.81932929635539</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7495229108768134</v>
+        <v>0.7923713712471462</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.40677299349385</v>
+        <v>3.432482069716049</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.02213813033933</v>
+        <v>-2.834541354353278</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.765401976245074</v>
+        <v>1.840440686639494</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7495229108768134</v>
+        <v>0.7923713712471462</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.424327399220641</v>
+        <v>3.450036475442841</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.190614247309207</v>
+        <v>-3.003017471323156</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.689866576861706</v>
+        <v>1.764905287256127</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7215750751602327</v>
+        <v>0.7644235355305654</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.399413745195277</v>
+        <v>3.425122821417476</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.492814718447624</v>
+        <v>-2.305217942461573</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.950256085594201</v>
+        <v>2.025294795988622</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.6512270157898219</v>
+        <v>0.6940754761601546</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.338474606760892</v>
+        <v>3.364183682983092</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.470093614764472</v>
+        <v>-2.28249683877842</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.950008549564367</v>
+        <v>2.025047259958788</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.6512270157898219</v>
+        <v>0.6940754761601546</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.329138629257796</v>
+        <v>3.354847705479996</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.468368571474428</v>
+        <v>-2.280771795488376</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.109604692731554</v>
+        <v>2.184643403125975</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6529520590798656</v>
+        <v>0.6958005194501984</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.489079781082992</v>
+        <v>3.514788857305192</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.623149578252683</v>
+        <v>-2.435552802266631</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.084770112513898</v>
+        <v>2.159808822908319</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6195843850253895</v>
+        <v>0.6624328453957222</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.506136999143953</v>
+        <v>3.531846075366152</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.571714244868023</v>
+        <v>-2.384117468881972</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.102019601857307</v>
+        <v>2.177058312251728</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6710197184100491</v>
+        <v>0.7138681787803819</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.533673555164293</v>
+        <v>3.559382631386493</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.544763020541535</v>
+        <v>-2.357166244555484</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.122806245232644</v>
+        <v>2.197844955627065</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.6859000644377683</v>
+        <v>0.728748524808101</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.552607916425667</v>
+        <v>3.578316992647866</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.680716028597852</v>
+        <v>-2.4931192526118</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.252528174155077</v>
+        <v>2.327566884549498</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.6859000644377683</v>
+        <v>0.728748524808101</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.736711048570626</v>
+        <v>3.762420124792826</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.703124146402724</v>
+        <v>-2.515527370416672</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.235681621936122</v>
+        <v>2.310720332330543</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.6859000644377683</v>
+        <v>0.728748524808101</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.728827743473619</v>
+        <v>3.754536819695819</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.851129913882123</v>
+        <v>-2.663533137896072</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.178533314494</v>
+        <v>2.25357202488842</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.5991730555742268</v>
+        <v>0.6420215159445596</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.678845537705132</v>
+        <v>3.704554613927332</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.860570839770653</v>
+        <v>-2.672974063784602</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.231010661860434</v>
+        <v>2.306049372254855</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7216001731176183</v>
+        <v>0.764448633487951</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.808555525953014</v>
+        <v>3.834264602175214</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.859284076231097</v>
+        <v>-2.671687300245045</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.234416461821558</v>
+        <v>2.309455172215978</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7228869366571749</v>
+        <v>0.7657353970275076</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.812218678622049</v>
+        <v>3.837927754844249</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.860841130220388</v>
+        <v>-2.673244354234336</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.231905453119617</v>
+        <v>2.306944163514037</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7228869366571749</v>
+        <v>0.7657353970275076</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.810330491515824</v>
+        <v>3.836039567738024</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.868113015743853</v>
+        <v>-2.680516239757801</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.223816928513093</v>
+        <v>2.298855638907514</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.71561505113371</v>
+        <v>0.7584635115040428</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.800787589804608</v>
+        <v>3.826496666026807</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.866271996685601</v>
+        <v>-2.67867522069955</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.222987346346546</v>
+        <v>2.298026056740967</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7168832778051785</v>
+        <v>0.7597317381755112</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.799982536017641</v>
+        <v>3.825691612239841</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.873180702185282</v>
+        <v>-2.68558392619923</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.233297271012592</v>
+        <v>2.308335981407013</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7168832778051785</v>
+        <v>0.7597317381755112</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.81305594288356</v>
+        <v>3.838765019105759</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.874742345000142</v>
+        <v>-2.68714556901409</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.232672613886648</v>
+        <v>2.307711324281069</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7168832778051785</v>
+        <v>0.7597317381755112</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.81305594288356</v>
+        <v>3.838765019105759</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.902643132109615</v>
+        <v>-2.715046356123563</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.220036340169861</v>
+        <v>2.295075050564281</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6822863536622437</v>
+        <v>0.7251348140325764</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.790821829524801</v>
+        <v>3.816530905747</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.905676129622289</v>
+        <v>-2.718079353636237</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.21558758514199</v>
+        <v>2.290626295536411</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6792533561495697</v>
+        <v>0.7221018165199025</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.785766474994395</v>
+        <v>3.811475551216595</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.925737450898795</v>
+        <v>-2.738140674912744</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.274269016221891</v>
+        <v>2.349307726616312</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6591920348730627</v>
+        <v>0.7020404952433954</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.840435641818995</v>
+        <v>3.866144718041194</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.182458268893619</v>
+        <v>-2.994861492907568</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.311892408025809</v>
+        <v>2.386931118420229</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5507774607292478</v>
+        <v>0.5936259210995806</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.915698616334553</v>
+        <v>3.941407692556752</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,45 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.874272178266801</v>
+        <v>3.668303164622231</v>
       </c>
       <c r="C2017" t="n">
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.33644468666976</v>
+        <v>-3.148847910683708</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.319278110060992</v>
+        <v>2.394316820455413</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5507774607292478</v>
+        <v>0.5936259210995806</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.984678885480193</v>
+        <v>4.010387961702392</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="2" t="n">
+        <v>45480</v>
+      </c>
+      <c r="B2018" t="n">
+        <v>3.868752033616595</v>
+      </c>
+      <c r="C2018" t="n">
+        <v>3.929625487010767</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>-3.148847910683708</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>2.394316820455413</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>0.5936259210995806</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>3.922689283997134</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -854,27 +854,27 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.0%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>461.1%</t>
+          <t>458.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-476.5%</t>
+          <t>-501.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-136.8%</t>
+          <t>-146.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-122.5%</t>
+          <t>-101.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>-180.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-53.8%</t>
+          <t>-63.2%</t>
         </is>
       </c>
     </row>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.927171457262393</v>
+        <v>-7.161129235942263</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3162913075663902</v>
+        <v>0.2227081960944424</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.9102463741854541</v>
+        <v>-1.056936767473763</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.541368490273823</v>
+        <v>2.453354254300837</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.779231415854793</v>
+        <v>-7.013189194534664</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2555884014412624</v>
+        <v>0.1620052899693145</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8899254582768965</v>
+        <v>-1.036615851565205</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.43368211713079</v>
+        <v>2.345667881157804</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.726261893600805</v>
+        <v>-6.960219672280675</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2680622240893795</v>
+        <v>0.1744791126174317</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8369559360229076</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.456749844229705</v>
+        <v>2.36873560825672</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.682713486830115</v>
+        <v>-6.916671265509985</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2785209747025625</v>
+        <v>0.1849378632306147</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8369559360229076</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.449789232134612</v>
+        <v>2.361774996161627</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.440565093376256</v>
+        <v>-6.674522872056126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3898426864652489</v>
+        <v>0.296259574993301</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8369559360229076</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.464251586515755</v>
+        <v>2.37623735054277</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.332305956253735</v>
+        <v>-6.566263734933605</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4276784617734526</v>
+        <v>0.3340953503015047</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8369559360229076</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.45878370697495</v>
+        <v>2.370769471001965</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.209014821436604</v>
+        <v>-6.442972600116474</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4744930097108822</v>
+        <v>0.3809098982389338</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7136648012057771</v>
+        <v>-0.8603551944940857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.530256481875805</v>
+        <v>2.44224224590282</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.187865622533161</v>
+        <v>-6.421823401213031</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4906536675095845</v>
+        <v>0.3970705560376366</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6925156023023338</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.550646979455196</v>
+        <v>2.462632743482211</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.944100180549716</v>
+        <v>-6.178057959229586</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.583940552650013</v>
+        <v>0.4903574411780647</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6925156023023338</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.546427687802247</v>
+        <v>2.458413451829262</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.842337360272421</v>
+        <v>-6.076295138952291</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6267699946809469</v>
+        <v>0.533186883208999</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6792965339099051</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.55648344275772</v>
+        <v>2.468469206784735</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.592486966323347</v>
+        <v>-5.826444745003217</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7194522272442789</v>
+        <v>0.6258691157723311</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6792965339099051</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.549225517741422</v>
+        <v>2.461211281768437</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.416594873855914</v>
+        <v>-5.650552652535785</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.793408187751901</v>
+        <v>0.6998250762799523</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6792965339099051</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.552824641262071</v>
+        <v>2.464810405289086</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.24514841083345</v>
+        <v>-5.479106189513321</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.87531427901544</v>
+        <v>0.7817311675434917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5078500708874419</v>
+        <v>-0.6545404641757505</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.669020025130103</v>
+        <v>2.581005789157117</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.170858845095111</v>
+        <v>-5.404816623774982</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9040505829270726</v>
+        <v>0.8104674714551243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4335605051491027</v>
+        <v>-0.5802508984374113</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.712614242189403</v>
+        <v>2.624600006216418</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.107223102861177</v>
+        <v>-5.341180881541048</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9341996808749635</v>
+        <v>0.8406165694030152</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3699247629151681</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.755490488584081</v>
+        <v>2.667476252611096</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.995796343535257</v>
+        <v>-5.229754122215128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9599646433891273</v>
+        <v>0.8663815319171788</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3699247629151681</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.736684747367877</v>
+        <v>2.648670511394891</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.755365846730396</v>
+        <v>-4.989323625410267</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.057879918735949</v>
+        <v>0.9642968072640004</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1294942661103078</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.88268612207567</v>
+        <v>2.794671886102685</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.683123278559202</v>
+        <v>-4.917081057239073</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.090706259839247</v>
+        <v>0.9971231483672984</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1294942661103078</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.88661543591049</v>
+        <v>2.798601199937505</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.630124956277814</v>
+        <v>-4.864082734957685</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.112584172669142</v>
+        <v>1.019001061197194</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.07415800710836901</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.920495775228994</v>
+        <v>2.832481539256008</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.521320070798087</v>
+        <v>-4.755277849477958</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.153104198081026</v>
+        <v>1.059521086609078</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.07415800710836901</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.917493846448987</v>
+        <v>2.829479610476002</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.301299272761076</v>
+        <v>-4.535257051440947</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.242691554306445</v>
+        <v>1.149108442834496</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06706183795961124</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.003804790500389</v>
+        <v>2.915790554527404</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.168431583697799</v>
+        <v>-4.40238936237767</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.311732812733579</v>
+        <v>1.218149701261631</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.06706183795961124</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.019698973302213</v>
+        <v>2.931684737329228</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.0482585003333</v>
+        <v>-4.282216279013171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.36094789051968</v>
+        <v>1.267364779047732</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1872349213241102</v>
+        <v>0.04054452803580155</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.092948667761214</v>
+        <v>3.004934431788229</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.903586355233562</v>
+        <v>-4.137544133913433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.428904851121015</v>
+        <v>1.335321739649067</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3319070664238476</v>
+        <v>0.185216673135539</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.189840057382496</v>
+        <v>3.101825821409511</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.963461182591255</v>
+        <v>-4.197418961271126</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.390992411579364</v>
+        <v>1.297409300107416</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2720322390661555</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.139952652369307</v>
+        <v>3.051938416396322</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.843640951680417</v>
+        <v>-4.077598730360289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.454209673177908</v>
+        <v>1.360626561705959</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2720322390661555</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.155241821603515</v>
+        <v>3.06722758563053</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.846110658142223</v>
+        <v>-4.080068436822095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.360865989915627</v>
+        <v>1.267282878443678</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2695625326043493</v>
+        <v>0.1228721393160407</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.061404197048873</v>
+        <v>2.973389961075888</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.914480844466233</v>
+        <v>-4.148438623146105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.252779776871324</v>
+        <v>1.159196665399375</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2788382316405643</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.986231477955904</v>
+        <v>2.898217241982918</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.92826889731328</v>
+        <v>-4.162226675993152</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.237701264364397</v>
+        <v>1.144118152892448</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2788382316405643</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.976668186587795</v>
+        <v>2.88865395061481</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.959262056641985</v>
+        <v>-4.193219835321857</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.050013565673302</v>
+        <v>0.9564304542013529</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2788382316405643</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.801377751628182</v>
+        <v>2.713363515655197</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.783787796849516</v>
+        <v>-4.017745575529387</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.124770501582077</v>
+        <v>1.031187390110128</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2788382316405643</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.80594498361997</v>
+        <v>2.717930747646984</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.894724049490764</v>
+        <v>-4.128681828170636</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.056138029286785</v>
+        <v>0.962554917814836</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2788382316405643</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.781687012381177</v>
+        <v>2.693672776408191</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.861060504018483</v>
+        <v>-4.095018282698354</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.072734832695603</v>
+        <v>0.9791517212236545</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3125017771128461</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.805016524884451</v>
+        <v>2.717002288911466</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.801207884814759</v>
+        <v>-4.035165663494631</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.106848266809225</v>
+        <v>1.013265155337276</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3125017771128461</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.815188911316584</v>
+        <v>2.727174675343599</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.714964421788382</v>
+        <v>-3.948922200468253</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.136291922593636</v>
+        <v>1.042708811121687</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3125017771128461</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.810135181890444</v>
+        <v>2.722120945917459</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.760271241187362</v>
+        <v>-3.994229019867233</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.10994497027857</v>
+        <v>1.016361858806621</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2716916141036153</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.777424859529431</v>
+        <v>2.689410623556446</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.789304345889664</v>
+        <v>-4.023262124569534</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.09888360143075</v>
+        <v>1.005300489958802</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2716916141036153</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.777976732562533</v>
+        <v>2.689962496589547</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.696493864438804</v>
+        <v>-3.930451643118675</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.06528048590246</v>
+        <v>0.9716973744305115</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3645020955544747</v>
+        <v>0.217811702266166</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.762935713324414</v>
+        <v>2.674921477351428</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.740883333768232</v>
+        <v>-3.974841112448102</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.04939817409529</v>
+        <v>0.9558150626233413</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.320112626225047</v>
+        <v>0.1734222329367384</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.738175507651358</v>
+        <v>2.650161271678373</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.628212115531982</v>
+        <v>-3.862169894211852</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.089542369901513</v>
+        <v>0.9959592584295645</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4327838444612972</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.800853947104831</v>
+        <v>2.712839711131846</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.515835114349309</v>
+        <v>-3.74979289302918</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.139984466205249</v>
+        <v>1.046401354733301</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4327838444612972</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.806345242935498</v>
+        <v>2.718331006962513</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.543615512250662</v>
+        <v>-3.777573290930533</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.140369508813247</v>
+        <v>1.046786397341299</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4050034465599441</v>
+        <v>0.2583130532716355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.801174205963226</v>
+        <v>2.71315996999024</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.626616793275941</v>
+        <v>-3.699525584447608</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9455247164037883</v>
+        <v>0.9163611999351216</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3864325620327704</v>
+        <v>0.2652653251991651</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.628387395247575</v>
+        <v>2.555687053147412</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.735230871719272</v>
+        <v>-3.808139662890939</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.022228745745662</v>
+        <v>0.9930652292769948</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3864325620327704</v>
+        <v>0.2652653251991651</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.74853705596678</v>
+        <v>2.675836713866617</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.699821833471129</v>
+        <v>-3.772730624642796</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.050905387147242</v>
+        <v>1.021741870678575</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3864325620327704</v>
+        <v>0.2652653251991651</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.763050082069103</v>
+        <v>2.69034973996894</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.661438170912978</v>
+        <v>-3.734346962084645</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.063678293512871</v>
+        <v>1.034514777044204</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4248162245909216</v>
+        <v>0.3036489877573162</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.783499720946363</v>
+        <v>2.710799378846199</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.484321840877812</v>
+        <v>-3.557230632049479</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.13125385437224</v>
+        <v>1.102090337903573</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4248162245909216</v>
+        <v>0.3036489877573162</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.780228749791665</v>
+        <v>2.707528407691502</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.529414085711358</v>
+        <v>-3.602322876883025</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.113900348200734</v>
+        <v>1.084736831732068</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3629201814215318</v>
+        <v>0.2417529445879265</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.743774515651944</v>
+        <v>2.671074173551781</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.35003866447259</v>
+        <v>-3.422947455644257</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.179437492002656</v>
+        <v>1.150273975533989</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5196969395922504</v>
+        <v>0.3985297027586451</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.83162754586079</v>
+        <v>2.758927203760627</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.395052877993197</v>
+        <v>-3.467961669164863</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.142239261926003</v>
+        <v>1.113075745457336</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4893480442776458</v>
+        <v>0.3681808074440405</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.794225664003616</v>
+        <v>2.721525321903453</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.662057388265632</v>
+        <v>-3.734966179437299</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.041129020155975</v>
+        <v>1.011965503687308</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2949850062346972</v>
+        <v>0.1738177694010919</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.683299403516793</v>
+        <v>2.61059906141663</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.763255169702805</v>
+        <v>-3.836163960874472</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9998538294776069</v>
+        <v>0.9706903130089404</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.226576192689378</v>
+        <v>0.1054089558557728</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.641458037286103</v>
+        <v>2.56875769518594</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.756744203088492</v>
+        <v>-3.829652994260159</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.000058177677649</v>
+        <v>0.9708946612089822</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.226576192689378</v>
+        <v>0.1054089558557728</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.63905799884042</v>
+        <v>2.566357656740257</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.737706075381195</v>
+        <v>-3.810614866552862</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.004198147968813</v>
+        <v>0.9750346315001459</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1683925813581835</v>
+        <v>0.04722534452457822</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.600672551249948</v>
+        <v>2.527972209149785</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.768832706531813</v>
+        <v>-3.84174149770348</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.169329364447246</v>
+        <v>1.140165847978579</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1683925813581835</v>
+        <v>0.04722534452457822</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.778254420188629</v>
+        <v>2.705554078088466</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.78269946786573</v>
+        <v>-3.855608259037397</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.164615988899813</v>
+        <v>1.135452472431146</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1305346646243605</v>
+        <v>0.009367427790755278</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.756372999134468</v>
+        <v>2.683672657034305</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.7378952963258</v>
+        <v>-3.810804087497467</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.18854618791271</v>
+        <v>1.159382671444044</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1305346646243605</v>
+        <v>0.009367427790755278</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.762381529531394</v>
+        <v>2.689681187431231</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.590152326090798</v>
+        <v>-3.663061117262465</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.326796023798733</v>
+        <v>1.297632507330067</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2983420218592437</v>
+        <v>0.1771747850256384</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.942218591664346</v>
+        <v>2.869518249564183</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.692167008622019</v>
+        <v>-3.765075799793686</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.288783772317726</v>
+        <v>1.259620255849059</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2983420218592437</v>
+        <v>0.1771747850256384</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.945012213195827</v>
+        <v>2.872311871095664</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.686014302569235</v>
+        <v>-3.758923093740901</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.291907203130498</v>
+        <v>1.262743686661831</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.304494727912028</v>
+        <v>0.1833274910784227</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.949366185219156</v>
+        <v>2.876665843118993</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.702823600719736</v>
+        <v>-3.775732391891403</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.284263960610408</v>
+        <v>1.255100444141741</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2876854297615263</v>
+        <v>0.1665181929279211</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.938361083068965</v>
+        <v>2.865660740968802</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.640525601943614</v>
+        <v>-3.713434393115281</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.375518713917677</v>
+        <v>1.34635519744901</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2876854297615263</v>
+        <v>0.1665181929279211</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.004696636865786</v>
+        <v>2.931996294765623</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.540666251398268</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.438735404278456</v>
+        <v>-3.511644195450123</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.164815665373139</v>
+        <v>1.135652148904472</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4857036219306807</v>
+        <v>0.3645363850970755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.832088424556677</v>
+        <v>2.759388082456514</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.610956483720444</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.36535730718972</v>
+        <v>-3.438266098361387</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.264457136530808</v>
+        <v>1.235293620062142</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5590817190194173</v>
+        <v>0.437914482185812</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.946405515132094</v>
+        <v>2.873705173031931</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.625584219836487</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.463097851814694</v>
+        <v>-3.536006642986361</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.239988654796862</v>
+        <v>1.210825138328195</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.543192440886437</v>
+        <v>0.4220252040528318</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.95149968436835</v>
+        <v>2.878799342268187</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.624120200661159</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.639435611937623</v>
+        <v>-3.71234440310929</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.167989531572362</v>
+        <v>1.138826015103696</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3668546807635076</v>
+        <v>0.2456874439299024</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.844233009119264</v>
+        <v>2.771532667019101</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.622611818701087</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.563013565505697</v>
+        <v>-3.635922356677364</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.197049968185061</v>
+        <v>1.167886451716395</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3668546807635076</v>
+        <v>0.2456874439299024</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.842724627159192</v>
+        <v>2.770024285059029</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.622474686136524</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.518640433867128</v>
+        <v>-3.591549225038795</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.214662088275925</v>
+        <v>1.185498571807258</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4112278124020762</v>
+        <v>0.290060575568471</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.86921137357777</v>
+        <v>2.796511031477606</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.616868480275114</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.395806212979961</v>
+        <v>-3.468715004151627</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.258189570769383</v>
+        <v>1.229026054300716</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4112278124020762</v>
+        <v>0.290060575568471</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.86360516771636</v>
+        <v>2.790904825616197</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.623250237302918</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.348150482418905</v>
+        <v>-3.421059273590572</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.283633620021609</v>
+        <v>1.254470103552942</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4588835429631319</v>
+        <v>0.3377163061295267</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.898580363080798</v>
+        <v>2.825880020980635</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.628142610677643</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.247632323920151</v>
+        <v>-3.320541115091817</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.328733256795836</v>
+        <v>1.299569740327169</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5594017014618864</v>
+        <v>0.4382344646282813</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.963783631554775</v>
+        <v>2.891083289454612</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.614897283153515</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.30829891432254</v>
+        <v>-3.381207705494206</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.291221293110752</v>
+        <v>1.262057776642086</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4777033847433527</v>
+        <v>0.3565361479097476</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.901519313999527</v>
+        <v>2.828818971899364</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.618994985764144</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.263460512714142</v>
+        <v>-3.336369303885808</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.31325435636474</v>
+        <v>1.284090839896073</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4822468176882222</v>
+        <v>0.3610795808546171</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.908343076377077</v>
+        <v>2.835642734276914</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.623155925395222</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.36421914847114</v>
+        <v>-3.437127939642807</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.277111841693019</v>
+        <v>1.247948325224352</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3934212489612168</v>
+        <v>0.2722540121276116</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.859208674771952</v>
+        <v>2.786508332671789</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.629035527923059</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.32001631138524</v>
+        <v>-3.392925102556906</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.300672579055216</v>
+        <v>1.271509062586549</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4376240860471172</v>
+        <v>0.3164568492135121</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.89160997955133</v>
+        <v>2.818909637451167</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.178629696091873</v>
+        <v>-3.42990413022035</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.35563722564181</v>
+        <v>1.255127451990419</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5118738522626326</v>
+        <v>0.3534307510048426</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.934569839749886</v>
+        <v>2.839503978995213</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.198687774956713</v>
+        <v>-3.44996220908519</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.398861759278914</v>
+        <v>1.298351985627523</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5118738522626326</v>
+        <v>0.3534307510048426</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.985817604932926</v>
+        <v>2.890751744178252</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.158757101778822</v>
+        <v>-3.410031535907299</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.413274733144323</v>
+        <v>1.312764959492932</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5518045254405229</v>
+        <v>0.393361424182733</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.008216713433913</v>
+        <v>2.91315085267924</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.107725009056294</v>
+        <v>-3.358999443184771</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.428635798471604</v>
+        <v>1.328126024820214</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.6028366181630509</v>
+        <v>0.4443935169052609</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.0337841973057</v>
+        <v>2.938718336551026</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.042500827929088</v>
+        <v>-3.293775262057566</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.471912875015192</v>
+        <v>1.371403101363801</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6680607992902565</v>
+        <v>0.5096176980324665</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.090106110074728</v>
+        <v>2.995040249320054</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.005073807857955</v>
+        <v>-3.256348241986432</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.482844655342926</v>
+        <v>1.382334881691535</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6733123373194382</v>
+        <v>0.5148692360616481</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.089218005191518</v>
+        <v>2.994152144436844</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.025185463892663</v>
+        <v>-3.276459898021141</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.476056785260283</v>
+        <v>1.375547011608891</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6843396823168574</v>
+        <v>0.5258965810590673</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.09709120452121</v>
+        <v>3.002025343766536</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.971440649465458</v>
+        <v>-3.222715083593936</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.658112482052375</v>
+        <v>1.557602708400984</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6944029917573193</v>
+        <v>0.5359598904995293</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.263686961206698</v>
+        <v>3.168621100452023</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.947649080859316</v>
+        <v>-3.198923514987793</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.787742018712649</v>
+        <v>1.687232245061258</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.7181945603634616</v>
+        <v>0.5597514591056716</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.3980748115882</v>
+        <v>3.303008950833526</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.921564996595508</v>
+        <v>-3.172839430723986</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.789883628432032</v>
+        <v>1.689373854780641</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.7181945603634616</v>
+        <v>0.5597514591056716</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.389782787602059</v>
+        <v>3.294716926847385</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.843433815746561</v>
+        <v>-3.094708249875039</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.81932929635539</v>
+        <v>1.718819522703999</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7923713712471462</v>
+        <v>0.6339282699893561</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.432482069716049</v>
+        <v>3.337416208961375</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.834541354353278</v>
+        <v>-3.085815788481756</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.840440686639494</v>
+        <v>1.739930912988103</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7923713712471462</v>
+        <v>0.6339282699893561</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.450036475442841</v>
+        <v>3.354970614688167</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.003017471323156</v>
+        <v>-3.254291905451633</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.764905287256127</v>
+        <v>1.664395513604736</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7644235355305654</v>
+        <v>0.6059804342727754</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.425122821417476</v>
+        <v>3.330056960662802</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.305217942461573</v>
+        <v>-2.55649237659005</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.025294795988622</v>
+        <v>1.924785022337232</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.6940754761601546</v>
+        <v>0.5356323749023646</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.364183682983092</v>
+        <v>3.269117822228417</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.28249683877842</v>
+        <v>-2.533771272906898</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.025047259958788</v>
+        <v>1.924537486307397</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.6940754761601546</v>
+        <v>0.5356323749023646</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.354847705479996</v>
+        <v>3.259781844725322</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.280771795488376</v>
+        <v>-2.532046229616854</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.184643403125975</v>
+        <v>2.084133629474583</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6958005194501984</v>
+        <v>0.5373574181924083</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.514788857305192</v>
+        <v>3.419722996550517</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.435552802266631</v>
+        <v>-2.686827236395109</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.159808822908319</v>
+        <v>2.059299049256928</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6624328453957222</v>
+        <v>0.5039897441379322</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.531846075366152</v>
+        <v>3.436780214611479</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.384117468881972</v>
+        <v>-2.635391903010449</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.177058312251728</v>
+        <v>2.076548538600337</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7138681787803819</v>
+        <v>0.5554250775225918</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.559382631386493</v>
+        <v>3.464316770631819</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.357166244555484</v>
+        <v>-2.608440678683961</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.197844955627065</v>
+        <v>2.097335181975674</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.728748524808101</v>
+        <v>0.570305423550311</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.578316992647866</v>
+        <v>3.483251131893192</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.4931192526118</v>
+        <v>-2.744393686740278</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.327566884549498</v>
+        <v>2.227057110898107</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.728748524808101</v>
+        <v>0.570305423550311</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.762420124792826</v>
+        <v>3.667354264038152</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.515527370416672</v>
+        <v>-2.76680180454515</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.310720332330543</v>
+        <v>2.210210558679151</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.728748524808101</v>
+        <v>0.570305423550311</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.754536819695819</v>
+        <v>3.659470958941145</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.663533137896072</v>
+        <v>-2.914807572024549</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.25357202488842</v>
+        <v>2.153062251237029</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6420215159445596</v>
+        <v>0.4835784146867695</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.704554613927332</v>
+        <v>3.609488753172658</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.672974063784602</v>
+        <v>-2.924248497913079</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.306049372254855</v>
+        <v>2.205539598603464</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.764448633487951</v>
+        <v>0.606005532230161</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.834264602175214</v>
+        <v>3.73919874142054</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.671687300245045</v>
+        <v>-2.922961734373523</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.309455172215978</v>
+        <v>2.208945398564587</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7657353970275076</v>
+        <v>0.6072922957697175</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.837927754844249</v>
+        <v>3.742861894089574</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.673244354234336</v>
+        <v>-2.924518788362814</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.306944163514037</v>
+        <v>2.206434389862646</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7657353970275076</v>
+        <v>0.6072922957697175</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.836039567738024</v>
+        <v>3.74097370698335</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.680516239757801</v>
+        <v>-2.931790673886279</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.298855638907514</v>
+        <v>2.198345865256123</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7584635115040428</v>
+        <v>0.6000204102462527</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.826496666026807</v>
+        <v>3.731430805272133</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.67867522069955</v>
+        <v>-2.929949654828027</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.298026056740967</v>
+        <v>2.197516283089575</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7597317381755112</v>
+        <v>0.6012886369177212</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.825691612239841</v>
+        <v>3.730625751485166</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.68558392619923</v>
+        <v>-2.936858360327708</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.308335981407013</v>
+        <v>2.207826207755621</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7597317381755112</v>
+        <v>0.6012886369177212</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.838765019105759</v>
+        <v>3.743699158351085</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.68714556901409</v>
+        <v>-2.938420003142568</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.307711324281069</v>
+        <v>2.207201550629678</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7597317381755112</v>
+        <v>0.6012886369177212</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.838765019105759</v>
+        <v>3.743699158351085</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.715046356123563</v>
+        <v>-2.966320790252041</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.295075050564281</v>
+        <v>2.194565276912891</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7251348140325764</v>
+        <v>0.5666917127747864</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.816530905747</v>
+        <v>3.721465044992326</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.718079353636237</v>
+        <v>-2.969353787764715</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.290626295536411</v>
+        <v>2.19011652188502</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7221018165199025</v>
+        <v>0.5636587152621124</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.811475551216595</v>
+        <v>3.716409690461921</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.738140674912744</v>
+        <v>-2.989415109041222</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.349307726616312</v>
+        <v>2.248797952964921</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7020404952433954</v>
+        <v>0.5435973939856054</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.866144718041194</v>
+        <v>3.77107885728652</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.994861492907568</v>
+        <v>-3.246135927036045</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.386931118420229</v>
+        <v>2.286421344768838</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5936259210995806</v>
+        <v>0.4351828198417905</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.941407692556752</v>
+        <v>3.846341831802078</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622231</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.148847910683708</v>
+        <v>-3.400122344812186</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.394316820455413</v>
+        <v>2.293807046804022</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5936259210995806</v>
+        <v>0.4351828198417905</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.010387961702392</v>
+        <v>3.915322100947718</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.868752033616595</v>
+        <v>3.722950178447839</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.929625487010767</v>
+        <v>3.835461632907656</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.148847910683708</v>
+        <v>-3.400122344812186</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.394316820455413</v>
+        <v>2.293807046804022</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5936259210995806</v>
+        <v>0.4351828198417905</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.922689283997134</v>
+        <v>3.828525429894023</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-69.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.3%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.6%</t>
+          <t>-526.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-146.8%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-101.7%</t>
+          <t>-112.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-180.5%</t>
+          <t>-177.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-93.1%</t>
         </is>
       </c>
     </row>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.829433643991976</v>
+        <v>-9.921813456107653</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7533856917957609</v>
+        <v>-0.7903376166420317</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.196054424866247</v>
+        <v>-2.141317543355914</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.861111535195029</v>
+        <v>1.893953664101228</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.704854987654384</v>
+        <v>-9.797234799770061</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7024150847046653</v>
+        <v>-0.7393670095509361</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.196054424866247</v>
+        <v>-2.141317543355914</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.862250679751088</v>
+        <v>1.895092808657287</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.757750275698671</v>
+        <v>-9.850130087814348</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7209394257602724</v>
+        <v>-0.7578913506065432</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.191099078777801</v>
+        <v>-2.136362197267468</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.867857661566263</v>
+        <v>1.900699790472463</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.68561710041079</v>
+        <v>-9.777996912526467</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6863524514064832</v>
+        <v>-0.723304376252754</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.191099078777801</v>
+        <v>-2.136362197267468</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.8735913658049</v>
+        <v>1.906433494711099</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.614250707801142</v>
+        <v>-9.706630519916819</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6675431567564898</v>
+        <v>-0.7044950816027606</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.119732686168153</v>
+        <v>-2.064995804657821</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.906673938976823</v>
+        <v>1.939516067883023</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.520791673815918</v>
+        <v>-9.613171485931595</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6400430244753075</v>
+        <v>-0.6769949493215783</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.119732686168153</v>
+        <v>-2.064995804657821</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.896790457663916</v>
+        <v>1.929632586570115</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.25354987294752</v>
+        <v>-9.345929685063197</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5349808646273222</v>
+        <v>-0.5719327894735931</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.119732686168153</v>
+        <v>-2.064995804657821</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.894955897164542</v>
+        <v>1.927798026070741</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.155642834271029</v>
+        <v>-9.248022646386707</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4961183641301865</v>
+        <v>-0.5330702889764574</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.051746936307596</v>
+        <v>-1.997010054797264</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.935447032107415</v>
+        <v>1.968289161013614</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.131689293295072</v>
+        <v>-9.224069105410749</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.48586844159431</v>
+        <v>-0.5228203664405808</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.027793395331639</v>
+        <v>-1.973056513821306</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.950487662838483</v>
+        <v>1.983329791744683</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.867629354972275</v>
+        <v>-8.960009167087952</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3935047824269433</v>
+        <v>-0.4304567072732142</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.763733457008843</v>
+        <v>-1.70899657549851</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.095663309670408</v>
+        <v>2.128505438576608</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.160549731467437</v>
+        <v>-8.252929543583114</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1134599666853093</v>
+        <v>-0.1504118915315802</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.763733457008843</v>
+        <v>-1.70899657549851</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.092876276010108</v>
+        <v>2.125718404916308</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.120365433101247</v>
+        <v>-8.212745245216924</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.09704262345099179</v>
+        <v>-0.1339945482972627</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.723549158642652</v>
+        <v>-1.668812277132319</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.117330478917664</v>
+        <v>2.150172607823863</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.956965562161884</v>
+        <v>-8.049345374277561</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.03231585385448987</v>
+        <v>-0.06926777870076029</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.56014928770329</v>
+        <v>-1.505412406192957</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.214737222702038</v>
+        <v>2.247579351608238</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.723484339932286</v>
+        <v>-7.815864152047962</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.06900106387520211</v>
+        <v>0.03204913902893169</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.326668065473691</v>
+        <v>-1.271931183963358</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.362750384877649</v>
+        <v>2.395592513783849</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.573817948924771</v>
+        <v>-7.666197761040447</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1259754099652488</v>
+        <v>0.0890234851189784</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.233764574231155</v>
+        <v>-1.179027692720822</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.415600269310212</v>
+        <v>2.448442398216411</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.441542475293884</v>
+        <v>-7.533922287409561</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1742530861646308</v>
+        <v>0.1373011613183599</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.101489100600269</v>
+        <v>-1.046752219089936</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.490333040235771</v>
+        <v>2.523175169141971</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.285804142734142</v>
+        <v>-7.378183954849819</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2393634798761641</v>
+        <v>0.2024115550298937</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.9457507680405269</v>
+        <v>-0.8910138865301941</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.586591100459253</v>
+        <v>2.619433229365452</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.036804344050561</v>
+        <v>-7.129184156166238</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3518697405732554</v>
+        <v>0.3149178157269845</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.9457507680405269</v>
+        <v>-0.8910138865301941</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.599497441682911</v>
+        <v>2.632339570589111</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.142394333823666</v>
+        <v>-7.234774145939342</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1816578150647947</v>
+        <v>0.1447058902185243</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.051340757813631</v>
+        <v>-0.9966038763032985</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.40816751821983</v>
+        <v>2.441009647126029</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.161129235942263</v>
+        <v>-7.253509048057939</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2227081960944424</v>
+        <v>0.185756271248172</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.056936767473763</v>
+        <v>-1.00219988596343</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.453354254300837</v>
+        <v>2.486196383207037</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.013189194534664</v>
+        <v>-7.10556900665034</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1620052899693145</v>
+        <v>0.1250533651230441</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.036615851565205</v>
+        <v>-0.9818789700548722</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.345667881157804</v>
+        <v>2.378510010064004</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.960219672280675</v>
+        <v>-7.052599484396351</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1744791126174317</v>
+        <v>0.1375271877711612</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9289094478008834</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.36873560825672</v>
+        <v>2.401577737162919</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.916671265509985</v>
+        <v>-7.009051077625661</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1849378632306147</v>
+        <v>0.1479859383843443</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9289094478008834</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.361774996161627</v>
+        <v>2.394617125067826</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.674522872056126</v>
+        <v>-6.766902684171803</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.296259574993301</v>
+        <v>0.2593076501470306</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9289094478008834</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.37623735054277</v>
+        <v>2.409079479448969</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.566263734933605</v>
+        <v>-6.658643547049281</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3340953503015047</v>
+        <v>0.2971434254552343</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9289094478008834</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.370769471001965</v>
+        <v>2.403611599908164</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.442972600116474</v>
+        <v>-6.53535241223215</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3809098982389338</v>
+        <v>0.3439579733926634</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8603551944940857</v>
+        <v>-0.8056183129837529</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.44224224590282</v>
+        <v>2.475084374809019</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.421823401213031</v>
+        <v>-6.514203213328707</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3970705560376366</v>
+        <v>0.3601186311913658</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.7844691140803095</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.462632743482211</v>
+        <v>2.495474872388411</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.178057959229586</v>
+        <v>-6.270437771345263</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4903574411780647</v>
+        <v>0.4534055163317943</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.7844691140803095</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.458413451829262</v>
+        <v>2.491255580735461</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.076295138952291</v>
+        <v>-6.168674951067968</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.533186883208999</v>
+        <v>0.4962349583627281</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7712500456878808</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.468469206784735</v>
+        <v>2.501311335690934</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.826444745003217</v>
+        <v>-5.918824557118893</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6258691157723311</v>
+        <v>0.5889171909260602</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7712500456878808</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.461211281768437</v>
+        <v>2.494053410674637</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.650552652535785</v>
+        <v>-5.74293246465146</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6998250762799523</v>
+        <v>0.6628731514336823</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7712500456878808</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.464810405289086</v>
+        <v>2.497652534195285</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.479106189513321</v>
+        <v>-5.571486001628997</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7817311675434917</v>
+        <v>0.7447792426972213</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6545404641757505</v>
+        <v>-0.5998035826654177</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.581005789157117</v>
+        <v>2.613847918063317</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.404816623774982</v>
+        <v>-5.497196435890658</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8104674714551243</v>
+        <v>0.7735155466088539</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5802508984374113</v>
+        <v>-0.5255140169270784</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624600006216418</v>
+        <v>2.657442135122618</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.341180881541048</v>
+        <v>-5.433560693656723</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8406165694030152</v>
+        <v>0.8036646445567452</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.4618782746931439</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.667476252611096</v>
+        <v>2.700318381517295</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.229754122215128</v>
+        <v>-5.322133934330803</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8663815319171788</v>
+        <v>0.8294296070709088</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.4618782746931439</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.648670511394891</v>
+        <v>2.681512640301091</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.989323625410267</v>
+        <v>-5.081703437525943</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9642968072640004</v>
+        <v>0.9273448824177302</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.2214477778882836</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.794671886102685</v>
+        <v>2.827514015008885</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.917081057239073</v>
+        <v>-5.009460869354748</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9971231483672984</v>
+        <v>0.9601712235210282</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.2214477778882836</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.798601199937505</v>
+        <v>2.831443328843705</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.864082734957685</v>
+        <v>-4.95646254707336</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.019001061197194</v>
+        <v>0.9820491363509234</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.1661115188863448</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.832481539256008</v>
+        <v>2.865323668162208</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.755277849477958</v>
+        <v>-4.847657661593633</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.059521086609078</v>
+        <v>1.022569161762808</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.1661115188863448</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.829479610476002</v>
+        <v>2.862321739382202</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.535257051440947</v>
+        <v>-4.627636863556623</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.149108442834496</v>
+        <v>1.112156517988226</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.07962855532869739</v>
+        <v>-0.02489167381836455</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.915790554527404</v>
+        <v>2.948632683433604</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.40238936237767</v>
+        <v>-4.494769174493345</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.218149701261631</v>
+        <v>1.181197776415361</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.07962855532869739</v>
+        <v>-0.02489167381836455</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.931684737329228</v>
+        <v>2.964526866235427</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.282216279013171</v>
+        <v>-4.374596091128846</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.267364779047732</v>
+        <v>1.230412854201462</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.04054452803580155</v>
+        <v>0.0952814095461344</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.004934431788229</v>
+        <v>3.037776560694429</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137544133913433</v>
+        <v>-4.229923946029109</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.335321739649067</v>
+        <v>1.298369814802797</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.185216673135539</v>
+        <v>0.2399535546458718</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.101825821409511</v>
+        <v>3.134667950315711</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197418961271126</v>
+        <v>-4.289798773386801</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.297409300107416</v>
+        <v>1.260457375261146</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.1800787272881797</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.051938416396322</v>
+        <v>3.084780545302521</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077598730360289</v>
+        <v>-4.169978542475964</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.360626561705959</v>
+        <v>1.323674636859689</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.1800787272881797</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06722758563053</v>
+        <v>3.10006971453673</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.080068436822095</v>
+        <v>-4.17244824893777</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.267282878443678</v>
+        <v>1.230330953597408</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1228721393160407</v>
+        <v>0.1776090208263735</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.973389961075888</v>
+        <v>3.006232089982088</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148438623146105</v>
+        <v>-4.24081843526178</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.159196665399375</v>
+        <v>1.122244740553105</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1868847198625885</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.898217241982918</v>
+        <v>2.931059370889118</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162226675993152</v>
+        <v>-4.254606488108827</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144118152892448</v>
+        <v>1.107166228046178</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1868847198625885</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.88865395061481</v>
+        <v>2.92149607952101</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.193219835321857</v>
+        <v>-4.285599647437532</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9564304542013529</v>
+        <v>0.9194785293550827</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1868847198625885</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.713363515655197</v>
+        <v>2.746205644561396</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.017745575529387</v>
+        <v>-4.110125387645063</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.031187390110128</v>
+        <v>0.9942354652638583</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1868847198625885</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.717930747646984</v>
+        <v>2.750772876553184</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.128681828170636</v>
+        <v>-4.221061640286312</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.962554917814836</v>
+        <v>0.9256029929685659</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1868847198625885</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.693672776408191</v>
+        <v>2.726514905314391</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.095018282698354</v>
+        <v>-4.187398094814029</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9791517212236545</v>
+        <v>0.9421997963773843</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.2205482653348703</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.717002288911466</v>
+        <v>2.749844417817666</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.035165663494631</v>
+        <v>-4.127545475610306</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.013265155337276</v>
+        <v>0.9763132304910058</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.2205482653348703</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.727174675343599</v>
+        <v>2.760016804249798</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.948922200468253</v>
+        <v>-4.041302012583929</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.042708811121687</v>
+        <v>1.005756886275417</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.2205482653348703</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.722120945917459</v>
+        <v>2.754963074823658</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.994229019867233</v>
+        <v>-4.086608831982908</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.016361858806621</v>
+        <v>0.9794099339603508</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.1797381023256395</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689410623556446</v>
+        <v>2.722252752462646</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.023262124569534</v>
+        <v>-4.11564193668521</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.005300489958802</v>
+        <v>0.9683485651125321</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.1797381023256395</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689962496589547</v>
+        <v>2.722804625495747</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.930451643118675</v>
+        <v>-4.02283145523435</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9716973744305115</v>
+        <v>0.9347454495842416</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.217811702266166</v>
+        <v>0.2725485837764989</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.674921477351428</v>
+        <v>2.707763606257628</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.974841112448102</v>
+        <v>-4.067220924563777</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9558150626233413</v>
+        <v>0.9188631377770713</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.1734222329367384</v>
+        <v>0.2281591144470712</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.650161271678373</v>
+        <v>2.683003400584572</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862169894211852</v>
+        <v>-3.954549706327527</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9959592584295645</v>
+        <v>0.9590073335832945</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.3408303326833214</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.712839711131846</v>
+        <v>2.745681840038046</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.74979289302918</v>
+        <v>-3.842172705144855</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.046401354733301</v>
+        <v>1.009449429887031</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.3408303326833214</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.718331006962513</v>
+        <v>2.751173135868713</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.777573290930533</v>
+        <v>-3.869953103046208</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.046786397341299</v>
+        <v>1.009834472495029</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2583130532716355</v>
+        <v>0.3130499347819684</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.71315996999024</v>
+        <v>2.74600209889644</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.699525584447608</v>
+        <v>-3.952954384071487</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9163611999351216</v>
+        <v>0.8149896800855703</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2652653251991651</v>
+        <v>0.2944790502547946</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.555687053147412</v>
+        <v>2.573215288180789</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.808139662890939</v>
+        <v>-4.061568462514818</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9930652292769948</v>
+        <v>0.8916937094274433</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2652653251991651</v>
+        <v>0.2944790502547946</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.675836713866617</v>
+        <v>2.693364948899995</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.772730624642796</v>
+        <v>-4.026159424266675</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.021741870678575</v>
+        <v>0.9203703508290235</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2652653251991651</v>
+        <v>0.2944790502547946</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.69034973996894</v>
+        <v>2.707877975002318</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.734346962084645</v>
+        <v>-3.987775761708524</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.034514777044204</v>
+        <v>0.9331432571946525</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3036489877573162</v>
+        <v>0.3328627128129458</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.710799378846199</v>
+        <v>2.728327613879577</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.557230632049479</v>
+        <v>-3.810659431673358</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.102090337903573</v>
+        <v>1.000718818054021</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3036489877573162</v>
+        <v>0.3328627128129458</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.707528407691502</v>
+        <v>2.725056642724879</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.602322876883025</v>
+        <v>-3.855751676506904</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.084736831732068</v>
+        <v>0.9833653118825163</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2417529445879265</v>
+        <v>0.270966669643556</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.671074173551781</v>
+        <v>2.688602408585159</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.422947455644257</v>
+        <v>-3.676376255268136</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.150273975533989</v>
+        <v>1.048902455684438</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3985297027586451</v>
+        <v>0.4277434278142747</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.758927203760627</v>
+        <v>2.776455438794004</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.467961669164863</v>
+        <v>-3.721390468788742</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.113075745457336</v>
+        <v>1.011704225607785</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3681808074440405</v>
+        <v>0.3973945324996701</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.721525321903453</v>
+        <v>2.739053556936831</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.734966179437299</v>
+        <v>-3.988394979061177</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.011965503687308</v>
+        <v>0.9105939838377566</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1738177694010919</v>
+        <v>0.2030314944567215</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.61059906141663</v>
+        <v>2.628127296450008</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.836163960874472</v>
+        <v>-4.08959276049835</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9706903130089404</v>
+        <v>0.8693187931593889</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1054089558557728</v>
+        <v>0.1346226809114023</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.56875769518594</v>
+        <v>2.586285930219318</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.829652994260159</v>
+        <v>-4.083081793884038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9708946612089822</v>
+        <v>0.8695231413594307</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1054089558557728</v>
+        <v>0.1346226809114023</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.566357656740257</v>
+        <v>2.583885891773634</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.810614866552862</v>
+        <v>-4.06404366617674</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9750346315001459</v>
+        <v>0.8736631116505944</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.04722534452457822</v>
+        <v>0.07643906958020774</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.527972209149785</v>
+        <v>2.545500444183163</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.84174149770348</v>
+        <v>-4.095170297327359</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.140165847978579</v>
+        <v>1.038794328129028</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.04722534452457822</v>
+        <v>0.07643906958020774</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.705554078088466</v>
+        <v>2.723082313121843</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.855608259037397</v>
+        <v>-4.109037058661277</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.135452472431146</v>
+        <v>1.034080952581594</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.009367427790755278</v>
+        <v>0.0385811528463848</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.683672657034305</v>
+        <v>2.701200892067683</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.810804087497467</v>
+        <v>-4.064232887121347</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.159382671444044</v>
+        <v>1.058011151594492</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.009367427790755278</v>
+        <v>0.0385811528463848</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.689681187431231</v>
+        <v>2.707209422464609</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.663061117262465</v>
+        <v>-3.916489916886345</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.297632507330067</v>
+        <v>1.196260987480515</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1771747850256384</v>
+        <v>0.206388510081268</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.869518249564183</v>
+        <v>2.887046484597561</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.765075799793686</v>
+        <v>-4.018504599417565</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.259620255849059</v>
+        <v>1.158248735999507</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1771747850256384</v>
+        <v>0.206388510081268</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.872311871095664</v>
+        <v>2.889840106129042</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.758923093740901</v>
+        <v>-4.012351893364781</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.262743686661831</v>
+        <v>1.161372166812279</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1833274910784227</v>
+        <v>0.2125412161340522</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.876665843118993</v>
+        <v>2.894194078152371</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.775732391891403</v>
+        <v>-4.029161191515283</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.255100444141741</v>
+        <v>1.153728924292189</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1665181929279211</v>
+        <v>0.1957319179835506</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.865660740968802</v>
+        <v>2.88318897600218</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.713434393115281</v>
+        <v>-3.966863192739161</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.34635519744901</v>
+        <v>1.244983677599458</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1665181929279211</v>
+        <v>0.1957319179835506</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.931996294765623</v>
+        <v>2.949524529799001</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.540666251398268</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.511644195450123</v>
+        <v>-3.765072995074003</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.135652148904472</v>
+        <v>1.03428062905492</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3645363850970755</v>
+        <v>0.393750110152705</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.759388082456514</v>
+        <v>2.776916317489892</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.610956483720444</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.438266098361387</v>
+        <v>-3.691694897985267</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.235293620062142</v>
+        <v>1.13392210021259</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.437914482185812</v>
+        <v>0.4671282072414416</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.873705173031931</v>
+        <v>2.891233408065309</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.625584219836487</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.536006642986361</v>
+        <v>-3.789435442610241</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.210825138328195</v>
+        <v>1.109453618478643</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4220252040528318</v>
+        <v>0.4512389291084614</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.878799342268187</v>
+        <v>2.896327577301564</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.624120200661159</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.71234440310929</v>
+        <v>-3.96577320273317</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.138826015103696</v>
+        <v>1.037454495254143</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2456874439299024</v>
+        <v>0.274901168985532</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.771532667019101</v>
+        <v>2.789060902052478</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.622611818701087</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.635922356677364</v>
+        <v>-3.889351156301244</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.167886451716395</v>
+        <v>1.066514931866843</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2456874439299024</v>
+        <v>0.274901168985532</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.770024285059029</v>
+        <v>2.787552520092407</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.622474686136524</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.591549225038795</v>
+        <v>-3.844978024662675</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.185498571807258</v>
+        <v>1.084127051957706</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.290060575568471</v>
+        <v>0.3192743006241006</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.796511031477606</v>
+        <v>2.814039266510984</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.616868480275114</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.468715004151627</v>
+        <v>-3.722143803775507</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.229026054300716</v>
+        <v>1.127654534451164</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.290060575568471</v>
+        <v>0.3192743006241006</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.790904825616197</v>
+        <v>2.808433060649575</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.623250237302918</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.421059273590572</v>
+        <v>-3.674488073214452</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.254470103552942</v>
+        <v>1.15309858370339</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3377163061295267</v>
+        <v>0.3669300311851562</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.825880020980635</v>
+        <v>2.843408256014012</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.628142610677643</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.320541115091817</v>
+        <v>-3.573969914715697</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.299569740327169</v>
+        <v>1.198198220477617</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4382344646282813</v>
+        <v>0.4674481896839108</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.891083289454612</v>
+        <v>2.90861152448799</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.614897283153515</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.381207705494206</v>
+        <v>-3.634636505118086</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.262057776642086</v>
+        <v>1.160686256792534</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3565361479097476</v>
+        <v>0.3857498729653771</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.828818971899364</v>
+        <v>2.846347206932742</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.618994985764144</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.336369303885808</v>
+        <v>-3.589798103509688</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.284090839896073</v>
+        <v>1.182719320046521</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3610795808546171</v>
+        <v>0.3902933059102466</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.835642734276914</v>
+        <v>2.853170969310292</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.623155925395222</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.437127939642807</v>
+        <v>-3.690556739266686</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.247948325224352</v>
+        <v>1.1465768053748</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2722540121276116</v>
+        <v>0.3014677371832412</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.786508332671789</v>
+        <v>2.804036567705167</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405955</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.629035527923059</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.392925102556906</v>
+        <v>-3.646353902180786</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.271509062586549</v>
+        <v>1.170137542736997</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3164568492135121</v>
+        <v>0.3456705742691416</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.818909637451167</v>
+        <v>2.836437872484544</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.42990413022035</v>
+        <v>-3.683332929844229</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.255127451990419</v>
+        <v>1.153755932140868</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3534307510048426</v>
+        <v>0.3826444760604721</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.839503978995213</v>
+        <v>2.85703221402859</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.44996220908519</v>
+        <v>-3.703391008709069</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.298351985627523</v>
+        <v>1.196980465777971</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3534307510048426</v>
+        <v>0.3826444760604721</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.890751744178252</v>
+        <v>2.90827997921163</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.410031535907299</v>
+        <v>-3.663460335531179</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.312764959492932</v>
+        <v>1.211393439643381</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.393361424182733</v>
+        <v>0.4225751492383625</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.91315085267924</v>
+        <v>2.930679087712617</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475134</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.358999443184771</v>
+        <v>-3.612428242808651</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.328126024820214</v>
+        <v>1.226754504970662</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4443935169052609</v>
+        <v>0.4736072419608904</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.938718336551026</v>
+        <v>2.956246571584404</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.293775262057566</v>
+        <v>-3.547204061681446</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.371403101363801</v>
+        <v>1.270031581514249</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.5096176980324665</v>
+        <v>0.5388314230880961</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.995040249320054</v>
+        <v>3.012568484353432</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.256348241986432</v>
+        <v>-3.509777041610312</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.382334881691535</v>
+        <v>1.280963361841983</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.5148692360616481</v>
+        <v>0.5440829611172777</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.994152144436844</v>
+        <v>3.011680379470222</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.276459898021141</v>
+        <v>-3.52988869764502</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.375547011608891</v>
+        <v>1.27417549175934</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5258965810590673</v>
+        <v>0.5551103061146969</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.002025343766536</v>
+        <v>3.019553578799913</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.222715083593936</v>
+        <v>-3.476143883217815</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.557602708400984</v>
+        <v>1.456231188551432</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.5359598904995293</v>
+        <v>0.5651736155551589</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.168621100452023</v>
+        <v>3.186149335485401</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.198923514987793</v>
+        <v>-3.452352314611673</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687232245061258</v>
+        <v>1.585860725211707</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5597514591056716</v>
+        <v>0.5889651841613012</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.303008950833526</v>
+        <v>3.320537185866904</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.172839430723986</v>
+        <v>-3.426268230347865</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689373854780641</v>
+        <v>1.588002334931089</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5597514591056716</v>
+        <v>0.5889651841613012</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.294716926847385</v>
+        <v>3.312245161880763</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.094708249875039</v>
+        <v>-3.348137049498918</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.718819522703999</v>
+        <v>1.617448002854447</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6339282699893561</v>
+        <v>0.6631419950449857</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.337416208961375</v>
+        <v>3.354944443994753</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.085815788481756</v>
+        <v>-3.339244588105635</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.739930912988103</v>
+        <v>1.638559393138551</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6339282699893561</v>
+        <v>0.6631419950449857</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.354970614688167</v>
+        <v>3.372498849721544</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.254291905451633</v>
+        <v>-3.507720705075513</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.664395513604736</v>
+        <v>1.563023993755184</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.6059804342727754</v>
+        <v>0.635194159328405</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.330056960662802</v>
+        <v>3.34758519569618</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.55649237659005</v>
+        <v>-2.80992117621393</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.924785022337232</v>
+        <v>1.823413502487679</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5356323749023646</v>
+        <v>0.5648460999579943</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.269117822228417</v>
+        <v>3.286646057261795</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.533771272906898</v>
+        <v>-2.787200072530777</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.924537486307397</v>
+        <v>1.823165966457845</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5356323749023646</v>
+        <v>0.5648460999579943</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.259781844725322</v>
+        <v>3.2773100797587</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.532046229616854</v>
+        <v>-2.785475029240733</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.084133629474583</v>
+        <v>1.982762109625032</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.5373574181924083</v>
+        <v>0.566571143248038</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.419722996550517</v>
+        <v>3.437251231583895</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.686827236395109</v>
+        <v>-2.940256036018988</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.059299049256928</v>
+        <v>1.957927529407376</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.5039897441379322</v>
+        <v>0.5332034691935619</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.436780214611479</v>
+        <v>3.454308449644856</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.635391903010449</v>
+        <v>-2.888820702634329</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.076548538600337</v>
+        <v>1.975177018750785</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5554250775225918</v>
+        <v>0.5846388025782215</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.464316770631819</v>
+        <v>3.481845005665197</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.608440678683961</v>
+        <v>-2.861869478307841</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.097335181975674</v>
+        <v>1.995963662126122</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.570305423550311</v>
+        <v>0.5995191486059407</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.483251131893192</v>
+        <v>3.50077936692657</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.744393686740278</v>
+        <v>-2.997822486364157</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.227057110898107</v>
+        <v>2.125685591048555</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.570305423550311</v>
+        <v>0.5995191486059407</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.667354264038152</v>
+        <v>3.68488249907153</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.76680180454515</v>
+        <v>-3.020230604169029</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.210210558679151</v>
+        <v>2.1088390388296</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.570305423550311</v>
+        <v>0.5995191486059407</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.659470958941145</v>
+        <v>3.676999193974523</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.914807572024549</v>
+        <v>-3.168236371648429</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.153062251237029</v>
+        <v>2.051690731387477</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4835784146867695</v>
+        <v>0.5127921397423992</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.609488753172658</v>
+        <v>3.627016988206035</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.924248497913079</v>
+        <v>-3.177677297536959</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.205539598603464</v>
+        <v>2.104168078753912</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.606005532230161</v>
+        <v>0.6352192572857907</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.73919874142054</v>
+        <v>3.756726976453918</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.922961734373523</v>
+        <v>-3.176390533997402</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.208945398564587</v>
+        <v>2.107573878715035</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.6072922957697175</v>
+        <v>0.6365060208253472</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.742861894089574</v>
+        <v>3.760390129122952</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.924518788362814</v>
+        <v>-3.177947587986694</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.206434389862646</v>
+        <v>2.105062870013094</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.6072922957697175</v>
+        <v>0.6365060208253472</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.74097370698335</v>
+        <v>3.758501942016728</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.931790673886279</v>
+        <v>-3.185219473510158</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.198345865256123</v>
+        <v>2.096974345406571</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6000204102462527</v>
+        <v>0.6292341353018824</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.731430805272133</v>
+        <v>3.748959040305511</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.929949654828027</v>
+        <v>-3.183378454451907</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.197516283089575</v>
+        <v>2.096144763240023</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6012886369177212</v>
+        <v>0.6305023619733509</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.730625751485166</v>
+        <v>3.748153986518544</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.936858360327708</v>
+        <v>-3.190287159951588</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.207826207755621</v>
+        <v>2.10645468790607</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6012886369177212</v>
+        <v>0.6305023619733509</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.743699158351085</v>
+        <v>3.761227393384463</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.938420003142568</v>
+        <v>-3.191848802766447</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.207201550629678</v>
+        <v>2.105830030780126</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6012886369177212</v>
+        <v>0.6305023619733509</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.743699158351085</v>
+        <v>3.761227393384463</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.966320790252041</v>
+        <v>-3.21974958987592</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.194565276912891</v>
+        <v>2.093193757063339</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5666917127747864</v>
+        <v>0.5959054378304161</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.721465044992326</v>
+        <v>3.738993280025704</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.969353787764715</v>
+        <v>-3.222782587388594</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.19011652188502</v>
+        <v>2.088745002035468</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5636587152621124</v>
+        <v>0.5928724403177421</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.716409690461921</v>
+        <v>3.733937925495299</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.989415109041222</v>
+        <v>-3.242843908665101</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.248797952964921</v>
+        <v>2.147426433115369</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5435973939856054</v>
+        <v>0.5728111190412351</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.77107885728652</v>
+        <v>3.788607092319898</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.246135927036045</v>
+        <v>-3.499564726659925</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.286421344768838</v>
+        <v>2.185049824919286</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4351828198417905</v>
+        <v>0.4643965448974202</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.846341831802078</v>
+        <v>3.863870066835456</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.400122344812186</v>
+        <v>-3.653551144436066</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.293807046804022</v>
+        <v>2.19243552695447</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4351828198417905</v>
+        <v>0.4643965448974202</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.915322100947718</v>
+        <v>3.932850335981096</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.722950178447839</v>
+        <v>3.356626290950441</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.835461632907656</v>
+        <v>3.536672725787871</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.400122344812186</v>
+        <v>-3.653551144436066</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.293807046804022</v>
+        <v>2.19243552695447</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4351828198417905</v>
+        <v>0.4643965448974202</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.828525429894023</v>
+        <v>3.529736522774238</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.3%</t>
+          <t>-68.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>460.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-526.9%</t>
+          <t>-522.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-156.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-112.1%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-177.6%</t>
+          <t>-169.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-49.1%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.921813456107653</v>
+        <v>-9.829433643991976</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7903376166420317</v>
+        <v>-0.7533856917957609</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.141317543355914</v>
+        <v>-2.196054424866247</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.893953664101228</v>
+        <v>1.861111535195029</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.797234799770061</v>
+        <v>-9.704854987654384</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7393670095509361</v>
+        <v>-0.7024150847046653</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.141317543355914</v>
+        <v>-2.196054424866247</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.895092808657287</v>
+        <v>1.862250679751088</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.850130087814348</v>
+        <v>-9.757750275698671</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7578913506065432</v>
+        <v>-0.7209394257602724</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.136362197267468</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.900699790472463</v>
+        <v>1.867857661566263</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.777996912526467</v>
+        <v>-9.68561710041079</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.723304376252754</v>
+        <v>-0.6863524514064832</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.136362197267468</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.906433494711099</v>
+        <v>1.8735913658049</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.706630519916819</v>
+        <v>-9.614250707801142</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7044950816027606</v>
+        <v>-0.6675431567564898</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.064995804657821</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.939516067883023</v>
+        <v>1.906673938976823</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.613171485931595</v>
+        <v>-9.520791673815918</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6769949493215783</v>
+        <v>-0.6400430244753075</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.064995804657821</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.929632586570115</v>
+        <v>1.896790457663916</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.345929685063197</v>
+        <v>-9.25354987294752</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5719327894735931</v>
+        <v>-0.5349808646273222</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.064995804657821</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.927798026070741</v>
+        <v>1.894955897164542</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.248022646386707</v>
+        <v>-9.155642834271029</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5330702889764574</v>
+        <v>-0.4961183641301865</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.997010054797264</v>
+        <v>-2.051746936307596</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.968289161013614</v>
+        <v>1.935447032107415</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.224069105410749</v>
+        <v>-9.131689293295072</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5228203664405808</v>
+        <v>-0.48586844159431</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.973056513821306</v>
+        <v>-2.027793395331639</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.983329791744683</v>
+        <v>1.950487662838483</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.960009167087952</v>
+        <v>-8.867629354972275</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4304567072732142</v>
+        <v>-0.3935047824269433</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.70899657549851</v>
+        <v>-1.763733457008843</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.128505438576608</v>
+        <v>2.095663309670408</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.252929543583114</v>
+        <v>-8.160549731467437</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1504118915315802</v>
+        <v>-0.1134599666853093</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.70899657549851</v>
+        <v>-1.763733457008843</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.125718404916308</v>
+        <v>2.092876276010108</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.212745245216924</v>
+        <v>-8.120365433101247</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1339945482972627</v>
+        <v>-0.09704262345099179</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.668812277132319</v>
+        <v>-1.723549158642652</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.150172607823863</v>
+        <v>2.117330478917664</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.049345374277561</v>
+        <v>-7.956965562161884</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.06926777870076029</v>
+        <v>-0.03231585385448987</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.505412406192957</v>
+        <v>-1.56014928770329</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.247579351608238</v>
+        <v>2.214737222702038</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.815864152047962</v>
+        <v>-7.723484339932286</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.03204913902893169</v>
+        <v>0.06900106387520211</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.271931183963358</v>
+        <v>-1.326668065473691</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.395592513783849</v>
+        <v>2.362750384877649</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.666197761040447</v>
+        <v>-7.573817948924771</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.0890234851189784</v>
+        <v>0.1259754099652488</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.179027692720822</v>
+        <v>-1.233764574231155</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.448442398216411</v>
+        <v>2.415600269310212</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.533922287409561</v>
+        <v>-7.441542475293884</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1373011613183599</v>
+        <v>0.1742530861646308</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.046752219089936</v>
+        <v>-1.101489100600269</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.523175169141971</v>
+        <v>2.490333040235771</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.378183954849819</v>
+        <v>-7.285804142734142</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2024115550298937</v>
+        <v>0.2393634798761641</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.8910138865301941</v>
+        <v>-0.9457507680405269</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.619433229365452</v>
+        <v>2.586591100459253</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.129184156166238</v>
+        <v>-7.036804344050561</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3149178157269845</v>
+        <v>0.3518697405732554</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.8910138865301941</v>
+        <v>-0.9457507680405269</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.632339570589111</v>
+        <v>2.599497441682911</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.234774145939342</v>
+        <v>-7.142394333823666</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1447058902185243</v>
+        <v>0.1816578150647947</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.9966038763032985</v>
+        <v>-1.051340757813631</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.441009647126029</v>
+        <v>2.40816751821983</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.253509048057939</v>
+        <v>-7.161129235942263</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.185756271248172</v>
+        <v>0.2227081960944424</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.00219988596343</v>
+        <v>-1.056936767473763</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.486196383207037</v>
+        <v>2.453354254300837</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.10556900665034</v>
+        <v>-7.013189194534664</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1250533651230441</v>
+        <v>0.1620052899693145</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.9818789700548722</v>
+        <v>-1.036615851565205</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.378510010064004</v>
+        <v>2.345667881157804</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.052599484396351</v>
+        <v>-6.960219672280675</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1375271877711612</v>
+        <v>0.1744791126174317</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9289094478008834</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.401577737162919</v>
+        <v>2.36873560825672</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.009051077625661</v>
+        <v>-6.916671265509985</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1479859383843443</v>
+        <v>0.1849378632306147</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9289094478008834</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.394617125067826</v>
+        <v>2.361774996161627</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.766902684171803</v>
+        <v>-6.674522872056126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2593076501470306</v>
+        <v>0.296259574993301</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9289094478008834</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.409079479448969</v>
+        <v>2.37623735054277</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.658643547049281</v>
+        <v>-6.566263734933605</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2971434254552343</v>
+        <v>0.3340953503015047</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9289094478008834</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.403611599908164</v>
+        <v>2.370769471001965</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.53535241223215</v>
+        <v>-6.442972600116474</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3439579733926634</v>
+        <v>0.3809098982389338</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8056183129837529</v>
+        <v>-0.8603551944940857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.475084374809019</v>
+        <v>2.44224224590282</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.514203213328707</v>
+        <v>-6.421823401213031</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3601186311913658</v>
+        <v>0.3970705560376366</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7844691140803095</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.495474872388411</v>
+        <v>2.462632743482211</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.270437771345263</v>
+        <v>-6.178057959229586</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4534055163317943</v>
+        <v>0.4903574411780647</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7844691140803095</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.491255580735461</v>
+        <v>2.458413451829262</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.168674951067968</v>
+        <v>-6.076295138952291</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4962349583627281</v>
+        <v>0.533186883208999</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7712500456878808</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.501311335690934</v>
+        <v>2.468469206784735</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.918824557118893</v>
+        <v>-5.826444745003217</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5889171909260602</v>
+        <v>0.6258691157723311</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7712500456878808</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.494053410674637</v>
+        <v>2.461211281768437</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.74293246465146</v>
+        <v>-5.650552652535785</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6628731514336823</v>
+        <v>0.6998250762799523</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7712500456878808</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.497652534195285</v>
+        <v>2.464810405289086</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.571486001628997</v>
+        <v>-5.479106189513321</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7447792426972213</v>
+        <v>0.7817311675434917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5998035826654177</v>
+        <v>-0.6545404641757505</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.613847918063317</v>
+        <v>2.581005789157117</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.497196435890658</v>
+        <v>-5.404816623774982</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7735155466088539</v>
+        <v>0.8104674714551243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5255140169270784</v>
+        <v>-0.5802508984374113</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.657442135122618</v>
+        <v>2.624600006216418</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.433560693656723</v>
+        <v>-5.341180881541048</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8036646445567452</v>
+        <v>0.8406165694030152</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.4618782746931439</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.700318381517295</v>
+        <v>2.667476252611096</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.322133934330803</v>
+        <v>-5.229754122215128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8294296070709088</v>
+        <v>0.8663815319171788</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.4618782746931439</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.681512640301091</v>
+        <v>2.648670511394891</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.081703437525943</v>
+        <v>-4.989323625410267</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9273448824177302</v>
+        <v>0.9642968072640004</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2214477778882836</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.827514015008885</v>
+        <v>2.794671886102685</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.009460869354748</v>
+        <v>-4.917081057239073</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9601712235210282</v>
+        <v>0.9971231483672984</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2214477778882836</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.831443328843705</v>
+        <v>2.798601199937505</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.95646254707336</v>
+        <v>-4.864082734957685</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9820491363509234</v>
+        <v>1.019001061197194</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1661115188863448</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.865323668162208</v>
+        <v>2.832481539256008</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.847657661593633</v>
+        <v>-4.755277849477958</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.022569161762808</v>
+        <v>1.059521086609078</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1661115188863448</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.862321739382202</v>
+        <v>2.829479610476002</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.627636863556623</v>
+        <v>-4.535257051440947</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.112156517988226</v>
+        <v>1.149108442834496</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.02489167381836455</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.948632683433604</v>
+        <v>2.915790554527404</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.494769174493345</v>
+        <v>-4.40238936237767</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.181197776415361</v>
+        <v>1.218149701261631</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.02489167381836455</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.964526866235427</v>
+        <v>2.931684737329228</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.374596091128846</v>
+        <v>-4.282216279013171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.230412854201462</v>
+        <v>1.267364779047732</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.0952814095461344</v>
+        <v>0.04054452803580155</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.037776560694429</v>
+        <v>3.004934431788229</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.229923946029109</v>
+        <v>-4.137544133913433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.298369814802797</v>
+        <v>1.335321739649067</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.2399535546458718</v>
+        <v>0.185216673135539</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.134667950315711</v>
+        <v>3.101825821409511</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.289798773386801</v>
+        <v>-4.197418961271126</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.260457375261146</v>
+        <v>1.297409300107416</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1800787272881797</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.084780545302521</v>
+        <v>3.051938416396322</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.169978542475964</v>
+        <v>-4.077598730360289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.323674636859689</v>
+        <v>1.360626561705959</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1800787272881797</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.10006971453673</v>
+        <v>3.06722758563053</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.17244824893777</v>
+        <v>-4.080068436822095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.230330953597408</v>
+        <v>1.267282878443678</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1776090208263735</v>
+        <v>0.1228721393160407</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.006232089982088</v>
+        <v>2.973389961075888</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.24081843526178</v>
+        <v>-4.148438623146105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.122244740553105</v>
+        <v>1.159196665399375</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1868847198625885</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.931059370889118</v>
+        <v>2.898217241982918</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.254606488108827</v>
+        <v>-4.162226675993152</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.107166228046178</v>
+        <v>1.144118152892448</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1868847198625885</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.92149607952101</v>
+        <v>2.88865395061481</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.285599647437532</v>
+        <v>-4.193219835321857</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9194785293550827</v>
+        <v>0.9564304542013529</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1868847198625885</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.746205644561396</v>
+        <v>2.713363515655197</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.110125387645063</v>
+        <v>-4.017745575529387</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9942354652638583</v>
+        <v>1.031187390110128</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1868847198625885</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.750772876553184</v>
+        <v>2.717930747646984</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.221061640286312</v>
+        <v>-4.128681828170636</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9256029929685659</v>
+        <v>0.962554917814836</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1868847198625885</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.726514905314391</v>
+        <v>2.693672776408191</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.187398094814029</v>
+        <v>-4.095018282698354</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9421997963773843</v>
+        <v>0.9791517212236545</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.2205482653348703</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.749844417817666</v>
+        <v>2.717002288911466</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.127545475610306</v>
+        <v>-4.035165663494631</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9763132304910058</v>
+        <v>1.013265155337276</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.2205482653348703</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.760016804249798</v>
+        <v>2.727174675343599</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.041302012583929</v>
+        <v>-3.948922200468253</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.005756886275417</v>
+        <v>1.042708811121687</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.2205482653348703</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.754963074823658</v>
+        <v>2.722120945917459</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.086608831982908</v>
+        <v>-3.994229019867233</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9794099339603508</v>
+        <v>1.016361858806621</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1797381023256395</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.722252752462646</v>
+        <v>2.689410623556446</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.11564193668521</v>
+        <v>-4.023262124569534</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9683485651125321</v>
+        <v>1.005300489958802</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1797381023256395</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.722804625495747</v>
+        <v>2.689962496589547</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.02283145523435</v>
+        <v>-3.930451643118675</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9347454495842416</v>
+        <v>0.9716973744305115</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.2725485837764989</v>
+        <v>0.217811702266166</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.707763606257628</v>
+        <v>2.674921477351428</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.067220924563777</v>
+        <v>-3.974841112448102</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9188631377770713</v>
+        <v>0.9558150626233413</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.2281591144470712</v>
+        <v>0.1734222329367384</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.683003400584572</v>
+        <v>2.650161271678373</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.954549706327527</v>
+        <v>-3.862169894211852</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9590073335832945</v>
+        <v>0.9959592584295645</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3408303326833214</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.745681840038046</v>
+        <v>2.712839711131846</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.842172705144855</v>
+        <v>-3.74979289302918</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.009449429887031</v>
+        <v>1.046401354733301</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3408303326833214</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.751173135868713</v>
+        <v>2.718331006962513</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.869953103046208</v>
+        <v>-3.777573290930533</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.009834472495029</v>
+        <v>1.046786397341299</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3130499347819684</v>
+        <v>0.2583130532716355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.74600209889644</v>
+        <v>2.71315996999024</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.952954384071487</v>
+        <v>-3.860574571955812</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8149896800855703</v>
+        <v>0.8519416049318402</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2944790502547946</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.573215288180789</v>
+        <v>2.540373159274589</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.061568462514818</v>
+        <v>-3.969188650399143</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8916937094274433</v>
+        <v>0.9286456342737133</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2944790502547946</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.693364948899995</v>
+        <v>2.660522819993795</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.026159424266675</v>
+        <v>-3.933779612151</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9203703508290235</v>
+        <v>0.9573222756752935</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2944790502547946</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.707877975002318</v>
+        <v>2.675035846096118</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.987775761708524</v>
+        <v>-3.895395949592849</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9331432571946525</v>
+        <v>0.9700951820409225</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3328627128129458</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.728327613879577</v>
+        <v>2.695485484973378</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.810659431673358</v>
+        <v>-3.718279619557683</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.000718818054021</v>
+        <v>1.037670742900291</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3328627128129458</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.725056642724879</v>
+        <v>2.69221451381868</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.855751676506904</v>
+        <v>-3.763371864391228</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9833653118825163</v>
+        <v>1.020317236728786</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.270966669643556</v>
+        <v>0.2162297881332231</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.688602408585159</v>
+        <v>2.655760279678959</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.676376255268136</v>
+        <v>-3.58399644315246</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.048902455684438</v>
+        <v>1.085854380530708</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4277434278142747</v>
+        <v>0.3730065463039418</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.776455438794004</v>
+        <v>2.743613309887805</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.721390468788742</v>
+        <v>-3.629010656673067</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.011704225607785</v>
+        <v>1.048656150454055</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3973945324996701</v>
+        <v>0.3426576509893372</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.739053556936831</v>
+        <v>2.706211428030632</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.988394979061177</v>
+        <v>-3.896015166945502</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9105939838377566</v>
+        <v>0.9475459086840265</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2030314944567215</v>
+        <v>0.1482946129463886</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.628127296450008</v>
+        <v>2.595285167543808</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.08959276049835</v>
+        <v>-3.997212948382675</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8693187931593889</v>
+        <v>0.9062707180056591</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1346226809114023</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.586285930219318</v>
+        <v>2.553443801313118</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.083081793884038</v>
+        <v>-3.990701981768362</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8695231413594307</v>
+        <v>0.9064750662057008</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1346226809114023</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.583885891773634</v>
+        <v>2.551043762867435</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.06404366617674</v>
+        <v>-3.971663854061065</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8736631116505944</v>
+        <v>0.9106150364968646</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.07643906958020774</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.545500444183163</v>
+        <v>2.512658315276963</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.095170297327359</v>
+        <v>-4.002790485211683</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.038794328129028</v>
+        <v>1.075746252975298</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.07643906958020774</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.723082313121843</v>
+        <v>2.690240184215644</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.109037058661277</v>
+        <v>-4.0166572465456</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.034080952581594</v>
+        <v>1.071032877427865</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.0385811528463848</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.701200892067683</v>
+        <v>2.668358763161483</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.064232887121347</v>
+        <v>-3.878184159736368</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.058011151594492</v>
+        <v>1.132430642548483</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.0385811528463848</v>
+        <v>0.1223173581452838</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.707209422464609</v>
+        <v>2.757451145643949</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.916489916886345</v>
+        <v>-3.730441189501366</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.196260987480515</v>
+        <v>1.270680478434506</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.206388510081268</v>
+        <v>0.290124715380167</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.887046484597561</v>
+        <v>2.9372882077769</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.018504599417565</v>
+        <v>-3.832455872032587</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.158248735999507</v>
+        <v>1.232668226953499</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.206388510081268</v>
+        <v>0.290124715380167</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889840106129042</v>
+        <v>2.940081829308381</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.012351893364781</v>
+        <v>-3.826303165979803</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.161372166812279</v>
+        <v>1.235791657766271</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2125412161340522</v>
+        <v>0.2962774214329513</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.894194078152371</v>
+        <v>2.94443580133171</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.029161191515283</v>
+        <v>-3.843112464130304</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.153728924292189</v>
+        <v>1.228148415246181</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1957319179835506</v>
+        <v>0.2794681232824496</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.88318897600218</v>
+        <v>2.933430699181519</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.966863192739161</v>
+        <v>-3.780814465354182</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.244983677599458</v>
+        <v>1.31940316855345</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1957319179835506</v>
+        <v>0.2794681232824496</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.949524529799001</v>
+        <v>2.99976625297834</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.540666251398268</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.765072995074003</v>
+        <v>-3.579024267689024</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.03428062905492</v>
+        <v>1.108700120008911</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.393750110152705</v>
+        <v>0.477486315451604</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.776916317489892</v>
+        <v>2.827158040669231</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.610956483720444</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.691694897985267</v>
+        <v>-3.505646170600288</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.13392210021259</v>
+        <v>1.208341591166581</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4671282072414416</v>
+        <v>0.5508644125403406</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.891233408065309</v>
+        <v>2.941475131244648</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.625584219836487</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.789435442610241</v>
+        <v>-3.603386715225262</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.109453618478643</v>
+        <v>1.183873109432635</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4512389291084614</v>
+        <v>0.5349751344073603</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.896327577301564</v>
+        <v>2.946569300480903</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.624120200661159</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.96577320273317</v>
+        <v>-3.779724475348191</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.037454495254143</v>
+        <v>1.111873986208135</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.274901168985532</v>
+        <v>0.3586373742844309</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.789060902052478</v>
+        <v>2.839302625231817</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.622611818701087</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.889351156301244</v>
+        <v>-3.703302428916265</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.066514931866843</v>
+        <v>1.140934422820834</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.274901168985532</v>
+        <v>0.3586373742844309</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.787552520092407</v>
+        <v>2.837794243271746</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.622474686136524</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.844978024662675</v>
+        <v>-3.658929297277696</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.084127051957706</v>
+        <v>1.158546542911698</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3192743006241006</v>
+        <v>0.4030105059229995</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.814039266510984</v>
+        <v>2.864280989690323</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.616868480275114</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.722143803775507</v>
+        <v>-3.536095076390529</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.127654534451164</v>
+        <v>1.202074025405155</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3192743006241006</v>
+        <v>0.4030105059229995</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.808433060649575</v>
+        <v>2.858674783828914</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.623250237302918</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.674488073214452</v>
+        <v>-3.488439345829473</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.15309858370339</v>
+        <v>1.227518074657382</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3669300311851562</v>
+        <v>0.4506662364840552</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.843408256014012</v>
+        <v>2.893649979193352</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.628142610677643</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.573969914715697</v>
+        <v>-3.387921187330718</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.198198220477617</v>
+        <v>1.272617711431608</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4674481896839108</v>
+        <v>0.5511843949828097</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.90861152448799</v>
+        <v>2.958853247667329</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.614897283153515</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.634636505118086</v>
+        <v>-3.448587777733108</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.160686256792534</v>
+        <v>1.235105747746525</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3857498729653771</v>
+        <v>0.469486078264276</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.846347206932742</v>
+        <v>2.896588930112081</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.618994985764144</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.589798103509688</v>
+        <v>-3.40374937612471</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.182719320046521</v>
+        <v>1.257138811000513</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3902933059102466</v>
+        <v>0.4740295112091455</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.853170969310292</v>
+        <v>2.903412692489631</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.623155925395222</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.690556739266686</v>
+        <v>-3.504508011881708</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.1465768053748</v>
+        <v>1.220996296328791</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3014677371832412</v>
+        <v>0.3852039424821401</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.804036567705167</v>
+        <v>2.854278290884506</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.629035527923059</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.646353902180786</v>
+        <v>-3.460305174795808</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.170137542736997</v>
+        <v>1.244557033690989</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3456705742691416</v>
+        <v>0.4294067795680405</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.836437872484544</v>
+        <v>2.886679595663884</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.683332929844229</v>
+        <v>-3.497284202459251</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.153755932140868</v>
+        <v>1.228175423094859</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3826444760604721</v>
+        <v>0.4663806813593711</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.85703221402859</v>
+        <v>2.907273937207929</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.703391008709069</v>
+        <v>-3.517342281324091</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.196980465777971</v>
+        <v>1.271399956731963</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3826444760604721</v>
+        <v>0.4663806813593711</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.90827997921163</v>
+        <v>2.958521702390969</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.663460335531179</v>
+        <v>-3.477411608146201</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.211393439643381</v>
+        <v>1.285812930597372</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.4225751492383625</v>
+        <v>0.5063113545372614</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.930679087712617</v>
+        <v>2.980920810891956</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.612428242808651</v>
+        <v>-3.426379515423672</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.226754504970662</v>
+        <v>1.301173995924653</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4736072419608904</v>
+        <v>0.5573434472597893</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.956246571584404</v>
+        <v>3.006488294763743</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.547204061681446</v>
+        <v>-3.361155334296467</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.270031581514249</v>
+        <v>1.34445107246824</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.5388314230880961</v>
+        <v>0.622567628386995</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.012568484353432</v>
+        <v>3.062810207532772</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.509777041610312</v>
+        <v>-3.323728314225333</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.280963361841983</v>
+        <v>1.355382852795974</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.5440829611172777</v>
+        <v>0.6278191664161766</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.011680379470222</v>
+        <v>3.061922102649561</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.52988869764502</v>
+        <v>-3.343839970260042</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.27417549175934</v>
+        <v>1.348594982713331</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5551103061146969</v>
+        <v>0.6388465114135958</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.019553578799913</v>
+        <v>3.069795301979253</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.476143883217815</v>
+        <v>-3.290095155832837</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.456231188551432</v>
+        <v>1.530650679505424</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.5651736155551589</v>
+        <v>0.6489098208540578</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.186149335485401</v>
+        <v>3.236391058664741</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.452352314611673</v>
+        <v>-3.266303587226695</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.585860725211707</v>
+        <v>1.660280216165698</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5889651841613012</v>
+        <v>0.6727013894602001</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.320537185866904</v>
+        <v>3.370778909046243</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.426268230347865</v>
+        <v>-3.240219502962887</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.588002334931089</v>
+        <v>1.66242182588508</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5889651841613012</v>
+        <v>0.6727013894602001</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.312245161880763</v>
+        <v>3.362486885060102</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.348137049498918</v>
+        <v>-3.16208832211394</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.617448002854447</v>
+        <v>1.691867493808438</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6631419950449857</v>
+        <v>0.7468782003438846</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.354944443994753</v>
+        <v>3.405186167174092</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.339244588105635</v>
+        <v>-3.153195860720657</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.638559393138551</v>
+        <v>1.712978884092543</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6631419950449857</v>
+        <v>0.7468782003438846</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.372498849721544</v>
+        <v>3.422740572900884</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.507720705075513</v>
+        <v>-3.321671977690535</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.563023993755184</v>
+        <v>1.637443484709176</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.635194159328405</v>
+        <v>0.7189303646273039</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.34758519569618</v>
+        <v>3.397826918875519</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.80992117621393</v>
+        <v>-2.623872448828951</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.823413502487679</v>
+        <v>1.897832993441671</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5648460999579943</v>
+        <v>0.6485823052568931</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.286646057261795</v>
+        <v>3.336887780441135</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.787200072530777</v>
+        <v>-2.601151345145799</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.823165966457845</v>
+        <v>1.897585457411836</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5648460999579943</v>
+        <v>0.6485823052568931</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.2773100797587</v>
+        <v>3.327551802938039</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.785475029240733</v>
+        <v>-2.599426301855755</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.982762109625032</v>
+        <v>2.057181600579023</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.566571143248038</v>
+        <v>0.6503073485469368</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.437251231583895</v>
+        <v>3.487492954763235</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.940256036018988</v>
+        <v>-2.75420730863401</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.957927529407376</v>
+        <v>2.032347020361367</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.5332034691935619</v>
+        <v>0.6169396744924607</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.454308449644856</v>
+        <v>3.504550172824195</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.888820702634329</v>
+        <v>-2.70277197524935</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.975177018750785</v>
+        <v>2.049596509704776</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5846388025782215</v>
+        <v>0.6683750078771203</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.481845005665197</v>
+        <v>3.532086728844536</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.861869478307841</v>
+        <v>-2.675820750922862</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.995963662126122</v>
+        <v>2.070383153080114</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.5995191486059407</v>
+        <v>0.6832553539048395</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.50077936692657</v>
+        <v>3.551021090105909</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.997822486364157</v>
+        <v>-2.811773758979179</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.125685591048555</v>
+        <v>2.200105082002547</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.5995191486059407</v>
+        <v>0.6832553539048395</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.68488249907153</v>
+        <v>3.735124222250869</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.020230604169029</v>
+        <v>-2.834181876784051</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.1088390388296</v>
+        <v>2.183258529783591</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.5995191486059407</v>
+        <v>0.6832553539048395</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.676999193974523</v>
+        <v>3.727240917153862</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.168236371648429</v>
+        <v>-2.98218764426345</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.051690731387477</v>
+        <v>2.126110222341469</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.5127921397423992</v>
+        <v>0.596528345041298</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.627016988206035</v>
+        <v>3.677258711385375</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.177677297536959</v>
+        <v>-2.99162857015198</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.104168078753912</v>
+        <v>2.178587569707903</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.6352192572857907</v>
+        <v>0.7189554625846895</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.756726976453918</v>
+        <v>3.806968699633257</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.176390533997402</v>
+        <v>-2.990341806612424</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.107573878715035</v>
+        <v>2.181993369669027</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.6365060208253472</v>
+        <v>0.720242226124246</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.760390129122952</v>
+        <v>3.810631852302292</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.177947587986694</v>
+        <v>-2.991898860601715</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.105062870013094</v>
+        <v>2.179482360967086</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.6365060208253472</v>
+        <v>0.720242226124246</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.758501942016728</v>
+        <v>3.808743665196067</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.185219473510158</v>
+        <v>-2.99917074612518</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.096974345406571</v>
+        <v>2.171393836360562</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6292341353018824</v>
+        <v>0.7129703406007812</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.748959040305511</v>
+        <v>3.79920076348485</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.183378454451907</v>
+        <v>-2.997329727066929</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.096144763240023</v>
+        <v>2.170564254194015</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6305023619733509</v>
+        <v>0.7142385672722497</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.748153986518544</v>
+        <v>3.798395709697884</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.190287159951588</v>
+        <v>-3.004238432566609</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.10645468790607</v>
+        <v>2.180874178860061</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6305023619733509</v>
+        <v>0.7142385672722497</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.761227393384463</v>
+        <v>3.811469116563802</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.191848802766447</v>
+        <v>-3.005800075381469</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.105830030780126</v>
+        <v>2.180249521734117</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6305023619733509</v>
+        <v>0.7142385672722497</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.761227393384463</v>
+        <v>3.811469116563802</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.21974958987592</v>
+        <v>-3.033700862490942</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.093193757063339</v>
+        <v>2.16761324801733</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5959054378304161</v>
+        <v>0.6796416431293149</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.738993280025704</v>
+        <v>3.789235003205043</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.222782587388594</v>
+        <v>-3.036733860003616</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.088745002035468</v>
+        <v>2.163164492989459</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5928724403177421</v>
+        <v>0.6766086456166409</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.733937925495299</v>
+        <v>3.784179648674638</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.242843908665101</v>
+        <v>-3.056795181280123</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.147426433115369</v>
+        <v>2.221845924069361</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5728111190412351</v>
+        <v>0.6565473243401339</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.788607092319898</v>
+        <v>3.838848815499238</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.499564726659925</v>
+        <v>-3.313515999274947</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.185049824919286</v>
+        <v>2.259469315873278</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4643965448974202</v>
+        <v>0.548132750196319</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.863870066835456</v>
+        <v>3.914111790014795</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.653551144436066</v>
+        <v>-3.467502417051087</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.19243552695447</v>
+        <v>2.266855017908461</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4643965448974202</v>
+        <v>0.548132750196319</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.932850335981096</v>
+        <v>3.983092059160435</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.356626290950441</v>
+        <v>3.774923783888234</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.536672725787871</v>
+        <v>3.640263611162764</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.653551144436066</v>
+        <v>-3.611465840646872</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.19243552695447</v>
+        <v>2.195320850590268</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4643965448974202</v>
+        <v>0.548132750196319</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.529736522774238</v>
+        <v>3.969143261280556</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240707.xlsx
+++ b/tame_output/ON/bt/strategyON_20240707.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.7%</t>
+          <t>-523.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-157.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-82.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-197.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-66.1%</t>
         </is>
       </c>
     </row>
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.878184159736368</v>
+        <v>-3.888495400471685</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.132430642548483</v>
+        <v>1.128306146254357</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1223173581452838</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.757451145643949</v>
+        <v>2.674367293558409</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.730441189501366</v>
+        <v>-3.740752430236682</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.270680478434506</v>
+        <v>1.26655598214038</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.290124715380167</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.9372882077769</v>
+        <v>2.854204355691361</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.832455872032587</v>
+        <v>-3.842767112767903</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.232668226953499</v>
+        <v>1.228543730659372</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.290124715380167</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.940081829308381</v>
+        <v>2.856997977222842</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.826303165979803</v>
+        <v>-3.836614406715119</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.235791657766271</v>
+        <v>1.231667161472144</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2962774214329513</v>
+        <v>0.1578043346237194</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.94443580133171</v>
+        <v>2.861351949246171</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.843112464130304</v>
+        <v>-3.85342370486562</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.228148415246181</v>
+        <v>1.224023918952054</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2794681232824496</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.933430699181519</v>
+        <v>2.85034684709598</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.780814465354182</v>
+        <v>-3.791125706089499</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.31940316855345</v>
+        <v>1.315278672259323</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2794681232824496</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.99976625297834</v>
+        <v>2.916682400892801</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.540666251398268</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.579024267689024</v>
+        <v>-3.589335508424341</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.108700120008911</v>
+        <v>1.104575623714785</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.477486315451604</v>
+        <v>0.3390132286423722</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.827158040669231</v>
+        <v>2.744074188583692</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.610956483720444</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.505646170600288</v>
+        <v>-3.515957411335604</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.208341591166581</v>
+        <v>1.204217094872455</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5508644125403406</v>
+        <v>0.4123913257311087</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.941475131244648</v>
+        <v>2.858391279159109</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.625584219836487</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.603386715225262</v>
+        <v>-3.613697955960578</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.183873109432635</v>
+        <v>1.179748613138508</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5349751344073603</v>
+        <v>0.3965020475981285</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.946569300480903</v>
+        <v>2.863485448395365</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.624120200661159</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.779724475348191</v>
+        <v>-3.790035716083508</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.111873986208135</v>
+        <v>1.107749489914009</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3586373742844309</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.839302625231817</v>
+        <v>2.756218773146279</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.622611818701087</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.703302428916265</v>
+        <v>-3.713613669651581</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.140934422820834</v>
+        <v>1.136809926526708</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3586373742844309</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.837794243271746</v>
+        <v>2.754710391186207</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.622474686136524</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.658929297277696</v>
+        <v>-3.669240538013012</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.158546542911698</v>
+        <v>1.154422046617571</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4030105059229995</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.864280989690323</v>
+        <v>2.781197137604785</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.616868480275114</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.536095076390529</v>
+        <v>-3.546406317125845</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.202074025405155</v>
+        <v>1.197949529111029</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4030105059229995</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.858674783828914</v>
+        <v>2.775590931743375</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.623250237302918</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.488439345829473</v>
+        <v>-3.498750586564789</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.227518074657382</v>
+        <v>1.223393578363255</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4506662364840552</v>
+        <v>0.3121931496748234</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.893649979193352</v>
+        <v>2.810566127107812</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.628142610677643</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.387921187330718</v>
+        <v>-3.398232428066034</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.272617711431608</v>
+        <v>1.268493215137482</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5511843949828097</v>
+        <v>0.4127113081735779</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.958853247667329</v>
+        <v>2.87576939558179</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.614897283153515</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.448587777733108</v>
+        <v>-3.458899018468423</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.235105747746525</v>
+        <v>1.230981251452399</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.469486078264276</v>
+        <v>0.3310129914550443</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.896588930112081</v>
+        <v>2.813505078026542</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.618994985764144</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.40374937612471</v>
+        <v>-3.414060616860025</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.257138811000513</v>
+        <v>1.253014314706387</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4740295112091455</v>
+        <v>0.3355564243999137</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.903412692489631</v>
+        <v>2.820328840404092</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.623155925395222</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.504508011881708</v>
+        <v>-3.514819252617024</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.220996296328791</v>
+        <v>1.216871800034665</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3852039424821401</v>
+        <v>0.2467308556729083</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.854278290884506</v>
+        <v>2.771194438798967</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.629035527923059</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.460305174795808</v>
+        <v>-3.470616415531123</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.244557033690989</v>
+        <v>1.240432537396862</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4294067795680405</v>
+        <v>0.2909336927588088</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.886679595663884</v>
+        <v>2.803595743578345</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.627445528392307</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.497284202459251</v>
+        <v>-3.507595443194567</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.228175423094859</v>
+        <v>1.224050926800733</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4663806813593711</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.907273937207929</v>
+        <v>2.824190085122391</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.678693293575346</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.517342281324091</v>
+        <v>-3.527653522059407</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.271399956731963</v>
+        <v>1.267275460437836</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4663806813593711</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.958521702390969</v>
+        <v>2.87543785030543</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.677133998169599</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.477411608146201</v>
+        <v>-3.487722848881516</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.285812930597372</v>
+        <v>1.281688434303246</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5063113545372614</v>
+        <v>0.3678382677280296</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.980920810891956</v>
+        <v>2.897836958806417</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.672082226407869</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.426379515423672</v>
+        <v>-3.436690756158988</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.301173995924653</v>
+        <v>1.297049499630527</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5573434472597893</v>
+        <v>0.4188703604505576</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.006488294763743</v>
+        <v>2.923404442678204</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.689269630500574</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.361155334296467</v>
+        <v>-3.371466575031783</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.34445107246824</v>
+        <v>1.340326576174114</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.622567628386995</v>
+        <v>0.4840945415777632</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.062810207532772</v>
+        <v>2.979726355447232</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.685230602799855</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.323728314225333</v>
+        <v>-3.334039554960649</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.355382852795974</v>
+        <v>1.351258356501848</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6278191664161766</v>
+        <v>0.4893460796069449</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.061922102649561</v>
+        <v>2.978838250564022</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.686487395131095</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.343839970260042</v>
+        <v>-3.354151210995358</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.348594982713331</v>
+        <v>1.344470486419205</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6388465114135958</v>
+        <v>0.5003734246043641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.069795301979253</v>
+        <v>2.986711449893714</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.847045166152306</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.290095155832837</v>
+        <v>-3.300406396568153</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.530650679505424</v>
+        <v>1.526526183211297</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6489098208540578</v>
+        <v>0.510436734044826</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.236391058664741</v>
+        <v>3.153307206579202</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.967158075370123</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.266303587226695</v>
+        <v>-3.27661482796201</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.660280216165698</v>
+        <v>1.656155719871572</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.6727013894602001</v>
+        <v>0.5342283026509683</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.370778909046243</v>
+        <v>3.287695056960704</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.958866051383982</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.240219502962887</v>
+        <v>-3.250530743698202</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.66242182588508</v>
+        <v>1.658297329590954</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.6727013894602001</v>
+        <v>0.5342283026509683</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.362486885060102</v>
+        <v>3.279403032974563</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.957059246967761</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.16208832211394</v>
+        <v>-3.172399562849256</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.691867493808438</v>
+        <v>1.687742997514312</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7468782003438846</v>
+        <v>0.6084051135346529</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.405186167174092</v>
+        <v>3.322102315088554</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.974613652694553</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.153195860720657</v>
+        <v>-3.163507101455973</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.712978884092543</v>
+        <v>1.708854387798417</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7468782003438846</v>
+        <v>0.6084051135346529</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.422740572900884</v>
+        <v>3.339656720815345</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.966468700099137</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.321671977690535</v>
+        <v>-3.33198321842585</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.637443484709176</v>
+        <v>1.633318988415049</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7189303646273039</v>
+        <v>0.5804572778180721</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.397826918875519</v>
+        <v>3.31474306678998</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.947738397286999</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.623872448828951</v>
+        <v>-2.634183689564267</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.897832993441671</v>
+        <v>1.893708497147544</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.6485823052568931</v>
+        <v>0.5101092184476614</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.336887780441135</v>
+        <v>3.253803928355596</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.938402419783903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.601151345145799</v>
+        <v>-2.611462585881115</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.897585457411836</v>
+        <v>1.89346096111771</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.6485823052568931</v>
+        <v>0.5101092184476614</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.327551802938039</v>
+        <v>3.2444679508525</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.097308545635072</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.599426301855755</v>
+        <v>-2.609737542591071</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.057181600579023</v>
+        <v>2.053057104284897</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6503073485469368</v>
+        <v>0.5118342617377052</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.487492954763235</v>
+        <v>3.404409102677695</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.134386368128719</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.75420730863401</v>
+        <v>-2.764518549369326</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.032347020361367</v>
+        <v>2.028222524067241</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6169396744924607</v>
+        <v>0.4784665876832291</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.504550172824195</v>
+        <v>3.421466320738657</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.131061724118264</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.70277197524935</v>
+        <v>-2.713083215984666</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.049596509704776</v>
+        <v>2.04547201341065</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6683750078771203</v>
+        <v>0.5299019210678888</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.532086728844536</v>
+        <v>3.449002876758998</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.141067877763005</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.675820750922862</v>
+        <v>-2.686131991658178</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.070383153080114</v>
+        <v>2.066258656785987</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.6832553539048395</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.551021090105909</v>
+        <v>3.467937238020371</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.325171009907965</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.811773758979179</v>
+        <v>-2.822084999714495</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.200105082002547</v>
+        <v>2.19598058570842</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.6832553539048395</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.735124222250869</v>
+        <v>3.65204037016533</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.317287704810958</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.834181876784051</v>
+        <v>-2.844493117519367</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.183258529783591</v>
+        <v>2.179134033489464</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.6832553539048395</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.727240917153862</v>
+        <v>3.644157065068323</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.319341704360596</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.98218764426345</v>
+        <v>-2.992498884998766</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.126110222341469</v>
+        <v>2.121985726047342</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.596528345041298</v>
+        <v>0.4580552582320665</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.677258711385375</v>
+        <v>3.594174859299836</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.375595422082443</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.99162857015198</v>
+        <v>-3.001939810887296</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.178587569707903</v>
+        <v>2.174463073413778</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7189554625846895</v>
+        <v>0.5804823757754579</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.806968699633257</v>
+        <v>3.723884847547718</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.378486516627744</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.990341806612424</v>
+        <v>-3.00065304734774</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.181993369669027</v>
+        <v>2.177868873374901</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.720242226124246</v>
+        <v>0.5817691393150145</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.810631852302292</v>
+        <v>3.727548000216753</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.376598329521519</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.991898860601715</v>
+        <v>-3.002210101337031</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.179482360967086</v>
+        <v>2.175357864672959</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.720242226124246</v>
+        <v>0.5817691393150145</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.808743665196067</v>
+        <v>3.725659813110528</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.371418559124381</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.99917074612518</v>
+        <v>-3.009481986860496</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.171393836360562</v>
+        <v>2.167269340066436</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7129703406007812</v>
+        <v>0.5744972537915498</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.79920076348485</v>
+        <v>3.716116911399312</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.369852569334534</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.997329727066929</v>
+        <v>-3.007640967802244</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.170564254194015</v>
+        <v>2.166439757899889</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7142385672722497</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.798395709697884</v>
+        <v>3.715311857612345</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.004238432566609</v>
+        <v>-3.014549673301925</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.180874178860061</v>
+        <v>2.176749682565935</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7142385672722497</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.811469116563802</v>
+        <v>3.728385264478264</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.382925976200452</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.005800075381469</v>
+        <v>-3.016111316116785</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.180249521734117</v>
+        <v>2.176125025439991</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7142385672722497</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.811469116563802</v>
+        <v>3.728385264478264</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.381450017327454</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.033700862490942</v>
+        <v>-3.044012103226258</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.16761324801733</v>
+        <v>2.163488751723204</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6796416431293149</v>
+        <v>0.5411685563200834</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.789235003205043</v>
+        <v>3.706151151119505</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.378214461304653</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.036733860003616</v>
+        <v>-3.047045100738932</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.163164492989459</v>
+        <v>2.159039996695333</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6766086456166409</v>
+        <v>0.5381355588074095</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.784179648674638</v>
+        <v>3.701095796589099</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.444920420895157</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.056795181280123</v>
+        <v>-3.067106422015438</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.221845924069361</v>
+        <v>2.217721427775234</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6565473243401339</v>
+        <v>0.5180742375309024</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.838848815499238</v>
+        <v>3.755764963413698</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.585232139897004</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.313515999274947</v>
+        <v>-3.323827240010262</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.259469315873278</v>
+        <v>2.255344819579151</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.548132750196319</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.914111790014795</v>
+        <v>3.831027937929257</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.654212409042644</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.467502417051087</v>
+        <v>-3.477813657786403</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.266855017908461</v>
+        <v>2.262730521614335</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.548132750196319</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.983092059160435</v>
+        <v>3.900008207074896</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.640263611162764</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.611465840646872</v>
+        <v>-3.622527147105356</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.195320850590268</v>
+        <v>2.190896328006875</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.548132750196319</v>
+        <v>0.2649461740681347</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.969143261280556</v>
+        <v>3.799231315603646</v>
       </c>
     </row>
   </sheetData>
